--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{954039AA-5E03-46E5-8A03-9C298DB24EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF3380BC-F162-4D2C-A71D-77AAA6AD0A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10448,7 +10448,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2C42157-DCA6-46AB-8B31-F04825DFD090}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{563DD795-8A85-44A9-991E-A60171C874CA}">
   <dimension ref="B3:H596"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF3380BC-F162-4D2C-A71D-77AAA6AD0A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B14F4C-C650-4554-AD5C-C3ADFFCF0682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10448,7 +10448,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{563DD795-8A85-44A9-991E-A60171C874CA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7B50FE1-747A-4961-B26E-F34367CD17D7}">
   <dimension ref="B3:H596"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B14F4C-C650-4554-AD5C-C3ADFFCF0682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06E9C18F-C586-4D09-A644-293BCFCB6D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10448,7 +10448,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7B50FE1-747A-4961-B26E-F34367CD17D7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A87C3462-F7BF-4E0B-9D7F-F042FEA7836B}">
   <dimension ref="B3:H596"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{873E0039-4C8F-4236-876C-DB63B61684C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B613666-6039-4F45-8DA3-BF879D070AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8486,7 +8486,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B0643D5-6E92-42CC-8DB8-7800570228E0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3A8FB7-91FB-421B-99AD-8ED792DDD208}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B613666-6039-4F45-8DA3-BF879D070AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B3E68E0-458F-4099-96FF-FCD1EAB08371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8486,7 +8486,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3A8FB7-91FB-421B-99AD-8ED792DDD208}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B56CF527-641A-4842-8431-7F7DED90FD43}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B3E68E0-458F-4099-96FF-FCD1EAB08371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{063D353A-997F-47D1-BB35-2395308D32B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8486,7 +8486,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B56CF527-641A-4842-8431-7F7DED90FD43}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E82FDCA-A7C2-44F4-AE8C-6702673CCC52}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{063D353A-997F-47D1-BB35-2395308D32B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55298B81-2FE5-4395-90F7-70F8B4F042B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8486,7 +8486,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E82FDCA-A7C2-44F4-AE8C-6702673CCC52}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E928BB5-10E5-4F10-A9B3-D7A6A5DB5782}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55298B81-2FE5-4395-90F7-70F8B4F042B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EFEAEF7-F55C-4F4F-BBAA-A10A0028884C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8486,7 +8486,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E928BB5-10E5-4F10-A9B3-D7A6A5DB5782}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0184135E-3D4C-41C2-8033-EFE07BE47FB7}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EFEAEF7-F55C-4F4F-BBAA-A10A0028884C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6ABC911-FF16-44C7-84A5-9E9EF6967F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8486,7 +8486,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0184135E-3D4C-41C2-8033-EFE07BE47FB7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7368D47D-AFC8-4B96-83FA-94F2C744656A}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6ABC911-FF16-44C7-84A5-9E9EF6967F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{782E66F8-36A2-4CD0-83E9-7CE7F2F91193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8486,7 +8486,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7368D47D-AFC8-4B96-83FA-94F2C744656A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F7827BE-230B-4D5E-AF1C-E8F7D10E385B}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{782E66F8-36A2-4CD0-83E9-7CE7F2F91193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB406A2-ED21-4E9F-BD92-F283AC881F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8486,7 +8486,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F7827BE-230B-4D5E-AF1C-E8F7D10E385B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{537E6F87-D110-4432-82FC-6C2235C5BB65}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB406A2-ED21-4E9F-BD92-F283AC881F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A3FC08A-4387-46D4-BE84-BBC86277F44E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8486,7 +8486,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{537E6F87-D110-4432-82FC-6C2235C5BB65}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C94B45-1B31-4752-9A97-01DE86B4EDAB}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A3FC08A-4387-46D4-BE84-BBC86277F44E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69A8AD4F-ABAA-46A7-B540-16AF592EADED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8486,7 +8486,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C94B45-1B31-4752-9A97-01DE86B4EDAB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C96A477-5E03-4EFE-8209-D5B68D1FFFE4}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69A8AD4F-ABAA-46A7-B540-16AF592EADED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C5AC65B-27B4-4E2C-9BB2-1BFE1D49708B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8486,7 +8486,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C96A477-5E03-4EFE-8209-D5B68D1FFFE4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDE19615-33A3-4FB3-B0BB-A25CDC1BABA9}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3D2033-7DC0-4E2D-90F4-A3EF23FAC7AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4EE9F2-B758-4B94-9DE1-5AC64EC39790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4934,7 +4934,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{984532DF-405A-45E2-BC43-D602C212AB98}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{339BD597-3794-4E4F-AB79-6967637FDF0F}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4EE9F2-B758-4B94-9DE1-5AC64EC39790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A14C977E-EA41-45B9-964D-06D3D3C162D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4934,7 +4934,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{339BD597-3794-4E4F-AB79-6967637FDF0F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E9032D3-52EB-47B7-B76B-E3944DA660DE}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A14C977E-EA41-45B9-964D-06D3D3C162D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF632AD-6C45-48D8-B09D-B92EF2811596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4934,7 +4934,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E9032D3-52EB-47B7-B76B-E3944DA660DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D43102C3-21A3-4A45-906E-7ED56530B825}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF632AD-6C45-48D8-B09D-B92EF2811596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8173B428-BD4E-460F-8789-CE8B8CEB2B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4934,7 +4934,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D43102C3-21A3-4A45-906E-7ED56530B825}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B412256-9F1B-46FB-9187-3B35B9BC43D2}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8173B428-BD4E-460F-8789-CE8B8CEB2B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18310F0B-C429-4AF5-B47C-3572FD3815DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -878,6 +878,12 @@
     <t>onshore wind electricity generation in cluster -- 14</t>
   </si>
   <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 15</t>
+  </si>
+  <si>
     <t>elc_won_016</t>
   </si>
   <si>
@@ -902,16 +908,10 @@
     <t>onshore wind electricity generation in cluster -- 20</t>
   </si>
   <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>onshore wind electricity generation in cluster -- 21</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>onshore wind electricity generation in cluster -- 22</t>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 23</t>
   </si>
   <si>
     <t>elc_won_024</t>
@@ -4934,7 +4934,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B412256-9F1B-46FB-9187-3B35B9BC43D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A15624E2-6411-44FD-A32C-6D12A6F53794}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18310F0B-C429-4AF5-B47C-3572FD3815DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122B39E6-8006-42DF-8ED4-7D0B738AD240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2655" uniqueCount="827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2787" uniqueCount="871">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -830,10 +830,154 @@
     <t>solar electricity generation in cluster -- 24</t>
   </si>
   <si>
-    <t>elc_spv_025</t>
-  </si>
-  <si>
-    <t>solar electricity generation in cluster -- 25</t>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>offwind electricity generation in cluster -- 1</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>offwind electricity generation in cluster -- 2</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>offwind electricity generation in cluster -- 3</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>offwind electricity generation in cluster -- 4</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>offwind electricity generation in cluster -- 5</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>offwind electricity generation in cluster -- 6</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>offwind electricity generation in cluster -- 7</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>offwind electricity generation in cluster -- 8</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>offwind electricity generation in cluster -- 9</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>offwind electricity generation in cluster -- 10</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>offwind electricity generation in cluster -- 11</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>offwind electricity generation in cluster -- 12</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>offwind electricity generation in cluster -- 13</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>offwind electricity generation in cluster -- 14</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>offwind electricity generation in cluster -- 15</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>offwind electricity generation in cluster -- 16</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>offwind electricity generation in cluster -- 17</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>offwind electricity generation in cluster -- 18</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>offwind electricity generation in cluster -- 19</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 1</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 2</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 3</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 4</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 5</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 6</t>
   </si>
   <si>
     <t>elc_won_007</t>
@@ -860,6 +1004,12 @@
     <t>onshore wind electricity generation in cluster -- 10</t>
   </si>
   <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 11</t>
+  </si>
+  <si>
     <t>elc_won_012</t>
   </si>
   <si>
@@ -896,34 +1046,16 @@
     <t>onshore wind electricity generation in cluster -- 17</t>
   </si>
   <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 18</t>
+  </si>
+  <si>
     <t>elc_won_019</t>
   </si>
   <si>
     <t>onshore wind electricity generation in cluster -- 19</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>onshore wind electricity generation in cluster -- 20</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>onshore wind electricity generation in cluster -- 23</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>onshore wind electricity generation in cluster -- 24</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>onshore wind electricity generation in cluster -- 25</t>
   </si>
   <si>
     <t>~fi_comm</t>
@@ -4934,13 +5066,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A15624E2-6411-44FD-A32C-6D12A6F53794}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51CF4A75-A2F4-4AB9-B852-3088D3B7DF51}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:8">
       <c r="B3" t="s">
-        <v>295</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="2:8">
@@ -4971,10 +5103,10 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>296</v>
+        <v>340</v>
       </c>
       <c r="D5" t="s">
-        <v>297</v>
+        <v>341</v>
       </c>
       <c r="E5" t="s">
         <v>25</v>
@@ -4983,7 +5115,7 @@
         <v>35</v>
       </c>
       <c r="G5" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H5" t="s">
         <v>216</v>
@@ -4994,10 +5126,10 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>299</v>
+        <v>343</v>
       </c>
       <c r="D6" t="s">
-        <v>300</v>
+        <v>344</v>
       </c>
       <c r="E6" t="s">
         <v>25</v>
@@ -5006,7 +5138,7 @@
         <v>35</v>
       </c>
       <c r="G6" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H6" t="s">
         <v>216</v>
@@ -5017,10 +5149,10 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>301</v>
+        <v>345</v>
       </c>
       <c r="D7" t="s">
-        <v>302</v>
+        <v>346</v>
       </c>
       <c r="E7" t="s">
         <v>25</v>
@@ -5029,7 +5161,7 @@
         <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H7" t="s">
         <v>216</v>
@@ -5040,10 +5172,10 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>303</v>
+        <v>347</v>
       </c>
       <c r="D8" t="s">
-        <v>304</v>
+        <v>348</v>
       </c>
       <c r="E8" t="s">
         <v>25</v>
@@ -5052,7 +5184,7 @@
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H8" t="s">
         <v>216</v>
@@ -5063,10 +5195,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>305</v>
+        <v>349</v>
       </c>
       <c r="D9" t="s">
-        <v>306</v>
+        <v>350</v>
       </c>
       <c r="E9" t="s">
         <v>25</v>
@@ -5075,7 +5207,7 @@
         <v>35</v>
       </c>
       <c r="G9" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H9" t="s">
         <v>216</v>
@@ -5086,10 +5218,10 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>307</v>
+        <v>351</v>
       </c>
       <c r="D10" t="s">
-        <v>308</v>
+        <v>352</v>
       </c>
       <c r="E10" t="s">
         <v>25</v>
@@ -5098,7 +5230,7 @@
         <v>35</v>
       </c>
       <c r="G10" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H10" t="s">
         <v>216</v>
@@ -5109,10 +5241,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>309</v>
+        <v>353</v>
       </c>
       <c r="D11" t="s">
-        <v>310</v>
+        <v>354</v>
       </c>
       <c r="E11" t="s">
         <v>25</v>
@@ -5121,7 +5253,7 @@
         <v>35</v>
       </c>
       <c r="G11" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H11" t="s">
         <v>216</v>
@@ -5132,10 +5264,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>311</v>
+        <v>355</v>
       </c>
       <c r="D12" t="s">
-        <v>312</v>
+        <v>356</v>
       </c>
       <c r="E12" t="s">
         <v>25</v>
@@ -5144,7 +5276,7 @@
         <v>35</v>
       </c>
       <c r="G12" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H12" t="s">
         <v>216</v>
@@ -5155,10 +5287,10 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>313</v>
+        <v>357</v>
       </c>
       <c r="D13" t="s">
-        <v>314</v>
+        <v>358</v>
       </c>
       <c r="E13" t="s">
         <v>25</v>
@@ -5167,7 +5299,7 @@
         <v>35</v>
       </c>
       <c r="G13" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H13" t="s">
         <v>216</v>
@@ -5178,10 +5310,10 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>315</v>
+        <v>359</v>
       </c>
       <c r="D14" t="s">
-        <v>316</v>
+        <v>360</v>
       </c>
       <c r="E14" t="s">
         <v>25</v>
@@ -5190,7 +5322,7 @@
         <v>35</v>
       </c>
       <c r="G14" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H14" t="s">
         <v>216</v>
@@ -5201,10 +5333,10 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>317</v>
+        <v>361</v>
       </c>
       <c r="D15" t="s">
-        <v>318</v>
+        <v>362</v>
       </c>
       <c r="E15" t="s">
         <v>25</v>
@@ -5213,7 +5345,7 @@
         <v>35</v>
       </c>
       <c r="G15" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H15" t="s">
         <v>216</v>
@@ -5224,10 +5356,10 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>319</v>
+        <v>363</v>
       </c>
       <c r="D16" t="s">
-        <v>320</v>
+        <v>364</v>
       </c>
       <c r="E16" t="s">
         <v>25</v>
@@ -5236,7 +5368,7 @@
         <v>35</v>
       </c>
       <c r="G16" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H16" t="s">
         <v>216</v>
@@ -5247,10 +5379,10 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>321</v>
+        <v>365</v>
       </c>
       <c r="D17" t="s">
-        <v>322</v>
+        <v>366</v>
       </c>
       <c r="E17" t="s">
         <v>25</v>
@@ -5259,7 +5391,7 @@
         <v>35</v>
       </c>
       <c r="G17" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H17" t="s">
         <v>216</v>
@@ -5270,10 +5402,10 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>323</v>
+        <v>367</v>
       </c>
       <c r="D18" t="s">
-        <v>324</v>
+        <v>368</v>
       </c>
       <c r="E18" t="s">
         <v>25</v>
@@ -5282,7 +5414,7 @@
         <v>35</v>
       </c>
       <c r="G18" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H18" t="s">
         <v>216</v>
@@ -5293,10 +5425,10 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>325</v>
+        <v>369</v>
       </c>
       <c r="D19" t="s">
-        <v>326</v>
+        <v>370</v>
       </c>
       <c r="E19" t="s">
         <v>25</v>
@@ -5305,7 +5437,7 @@
         <v>35</v>
       </c>
       <c r="G19" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H19" t="s">
         <v>216</v>
@@ -5316,10 +5448,10 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>327</v>
+        <v>371</v>
       </c>
       <c r="D20" t="s">
-        <v>328</v>
+        <v>372</v>
       </c>
       <c r="E20" t="s">
         <v>25</v>
@@ -5328,7 +5460,7 @@
         <v>35</v>
       </c>
       <c r="G20" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H20" t="s">
         <v>216</v>
@@ -5339,10 +5471,10 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>329</v>
+        <v>373</v>
       </c>
       <c r="D21" t="s">
-        <v>330</v>
+        <v>374</v>
       </c>
       <c r="E21" t="s">
         <v>25</v>
@@ -5351,7 +5483,7 @@
         <v>35</v>
       </c>
       <c r="G21" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H21" t="s">
         <v>216</v>
@@ -5362,10 +5494,10 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>331</v>
+        <v>375</v>
       </c>
       <c r="D22" t="s">
-        <v>332</v>
+        <v>376</v>
       </c>
       <c r="E22" t="s">
         <v>25</v>
@@ -5374,7 +5506,7 @@
         <v>35</v>
       </c>
       <c r="G22" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H22" t="s">
         <v>216</v>
@@ -5385,10 +5517,10 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>333</v>
+        <v>377</v>
       </c>
       <c r="D23" t="s">
-        <v>334</v>
+        <v>378</v>
       </c>
       <c r="E23" t="s">
         <v>25</v>
@@ -5397,7 +5529,7 @@
         <v>35</v>
       </c>
       <c r="G23" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H23" t="s">
         <v>216</v>
@@ -5408,10 +5540,10 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>335</v>
+        <v>379</v>
       </c>
       <c r="D24" t="s">
-        <v>336</v>
+        <v>380</v>
       </c>
       <c r="E24" t="s">
         <v>25</v>
@@ -5420,7 +5552,7 @@
         <v>35</v>
       </c>
       <c r="G24" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H24" t="s">
         <v>216</v>
@@ -5431,10 +5563,10 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>337</v>
+        <v>381</v>
       </c>
       <c r="D25" t="s">
-        <v>338</v>
+        <v>382</v>
       </c>
       <c r="E25" t="s">
         <v>25</v>
@@ -5443,7 +5575,7 @@
         <v>35</v>
       </c>
       <c r="G25" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H25" t="s">
         <v>216</v>
@@ -5454,10 +5586,10 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>339</v>
+        <v>383</v>
       </c>
       <c r="D26" t="s">
-        <v>340</v>
+        <v>384</v>
       </c>
       <c r="E26" t="s">
         <v>25</v>
@@ -5466,7 +5598,7 @@
         <v>35</v>
       </c>
       <c r="G26" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H26" t="s">
         <v>216</v>
@@ -5477,10 +5609,10 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>341</v>
+        <v>385</v>
       </c>
       <c r="D27" t="s">
-        <v>342</v>
+        <v>386</v>
       </c>
       <c r="E27" t="s">
         <v>25</v>
@@ -5489,7 +5621,7 @@
         <v>35</v>
       </c>
       <c r="G27" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H27" t="s">
         <v>216</v>
@@ -5500,10 +5632,10 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>343</v>
+        <v>387</v>
       </c>
       <c r="D28" t="s">
-        <v>344</v>
+        <v>388</v>
       </c>
       <c r="E28" t="s">
         <v>25</v>
@@ -5512,7 +5644,7 @@
         <v>35</v>
       </c>
       <c r="G28" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H28" t="s">
         <v>216</v>
@@ -5523,10 +5655,10 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>345</v>
+        <v>389</v>
       </c>
       <c r="D29" t="s">
-        <v>346</v>
+        <v>390</v>
       </c>
       <c r="E29" t="s">
         <v>25</v>
@@ -5535,7 +5667,7 @@
         <v>35</v>
       </c>
       <c r="G29" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H29" t="s">
         <v>216</v>
@@ -5546,10 +5678,10 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>347</v>
+        <v>391</v>
       </c>
       <c r="D30" t="s">
-        <v>348</v>
+        <v>392</v>
       </c>
       <c r="E30" t="s">
         <v>25</v>
@@ -5558,7 +5690,7 @@
         <v>35</v>
       </c>
       <c r="G30" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H30" t="s">
         <v>216</v>
@@ -5569,10 +5701,10 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>349</v>
+        <v>393</v>
       </c>
       <c r="D31" t="s">
-        <v>350</v>
+        <v>394</v>
       </c>
       <c r="E31" t="s">
         <v>25</v>
@@ -5581,7 +5713,7 @@
         <v>35</v>
       </c>
       <c r="G31" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H31" t="s">
         <v>216</v>
@@ -5592,10 +5724,10 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>351</v>
+        <v>395</v>
       </c>
       <c r="D32" t="s">
-        <v>352</v>
+        <v>396</v>
       </c>
       <c r="E32" t="s">
         <v>25</v>
@@ -5604,7 +5736,7 @@
         <v>35</v>
       </c>
       <c r="G32" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H32" t="s">
         <v>216</v>
@@ -5615,10 +5747,10 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>353</v>
+        <v>397</v>
       </c>
       <c r="D33" t="s">
-        <v>354</v>
+        <v>398</v>
       </c>
       <c r="E33" t="s">
         <v>25</v>
@@ -5627,7 +5759,7 @@
         <v>35</v>
       </c>
       <c r="G33" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H33" t="s">
         <v>216</v>
@@ -5638,10 +5770,10 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>355</v>
+        <v>399</v>
       </c>
       <c r="D34" t="s">
-        <v>356</v>
+        <v>400</v>
       </c>
       <c r="E34" t="s">
         <v>25</v>
@@ -5650,7 +5782,7 @@
         <v>35</v>
       </c>
       <c r="G34" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H34" t="s">
         <v>216</v>
@@ -5661,10 +5793,10 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>357</v>
+        <v>401</v>
       </c>
       <c r="D35" t="s">
-        <v>358</v>
+        <v>402</v>
       </c>
       <c r="E35" t="s">
         <v>25</v>
@@ -5673,7 +5805,7 @@
         <v>35</v>
       </c>
       <c r="G35" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H35" t="s">
         <v>216</v>
@@ -5684,10 +5816,10 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>359</v>
+        <v>403</v>
       </c>
       <c r="D36" t="s">
-        <v>360</v>
+        <v>404</v>
       </c>
       <c r="E36" t="s">
         <v>25</v>
@@ -5696,7 +5828,7 @@
         <v>35</v>
       </c>
       <c r="G36" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H36" t="s">
         <v>216</v>
@@ -5707,10 +5839,10 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>361</v>
+        <v>405</v>
       </c>
       <c r="D37" t="s">
-        <v>362</v>
+        <v>406</v>
       </c>
       <c r="E37" t="s">
         <v>25</v>
@@ -5719,7 +5851,7 @@
         <v>35</v>
       </c>
       <c r="G37" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H37" t="s">
         <v>216</v>
@@ -5730,10 +5862,10 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>363</v>
+        <v>407</v>
       </c>
       <c r="D38" t="s">
-        <v>364</v>
+        <v>408</v>
       </c>
       <c r="E38" t="s">
         <v>25</v>
@@ -5742,7 +5874,7 @@
         <v>35</v>
       </c>
       <c r="G38" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H38" t="s">
         <v>216</v>
@@ -5753,10 +5885,10 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>365</v>
+        <v>409</v>
       </c>
       <c r="D39" t="s">
-        <v>366</v>
+        <v>410</v>
       </c>
       <c r="E39" t="s">
         <v>25</v>
@@ -5765,7 +5897,7 @@
         <v>35</v>
       </c>
       <c r="G39" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H39" t="s">
         <v>216</v>
@@ -5776,10 +5908,10 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>367</v>
+        <v>411</v>
       </c>
       <c r="D40" t="s">
-        <v>368</v>
+        <v>412</v>
       </c>
       <c r="E40" t="s">
         <v>25</v>
@@ -5788,7 +5920,7 @@
         <v>35</v>
       </c>
       <c r="G40" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H40" t="s">
         <v>216</v>
@@ -5799,10 +5931,10 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>369</v>
+        <v>413</v>
       </c>
       <c r="D41" t="s">
-        <v>370</v>
+        <v>414</v>
       </c>
       <c r="E41" t="s">
         <v>25</v>
@@ -5811,7 +5943,7 @@
         <v>35</v>
       </c>
       <c r="G41" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H41" t="s">
         <v>216</v>
@@ -5822,10 +5954,10 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>371</v>
+        <v>415</v>
       </c>
       <c r="D42" t="s">
-        <v>372</v>
+        <v>416</v>
       </c>
       <c r="E42" t="s">
         <v>25</v>
@@ -5834,7 +5966,7 @@
         <v>35</v>
       </c>
       <c r="G42" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H42" t="s">
         <v>216</v>
@@ -5845,10 +5977,10 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>373</v>
+        <v>417</v>
       </c>
       <c r="D43" t="s">
-        <v>374</v>
+        <v>418</v>
       </c>
       <c r="E43" t="s">
         <v>25</v>
@@ -5857,7 +5989,7 @@
         <v>35</v>
       </c>
       <c r="G43" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H43" t="s">
         <v>216</v>
@@ -5868,10 +6000,10 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>375</v>
+        <v>419</v>
       </c>
       <c r="D44" t="s">
-        <v>376</v>
+        <v>420</v>
       </c>
       <c r="E44" t="s">
         <v>25</v>
@@ -5880,7 +6012,7 @@
         <v>35</v>
       </c>
       <c r="G44" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H44" t="s">
         <v>216</v>
@@ -5891,10 +6023,10 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>377</v>
+        <v>421</v>
       </c>
       <c r="D45" t="s">
-        <v>378</v>
+        <v>422</v>
       </c>
       <c r="E45" t="s">
         <v>25</v>
@@ -5903,7 +6035,7 @@
         <v>35</v>
       </c>
       <c r="G45" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H45" t="s">
         <v>216</v>
@@ -5914,10 +6046,10 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>379</v>
+        <v>423</v>
       </c>
       <c r="D46" t="s">
-        <v>380</v>
+        <v>424</v>
       </c>
       <c r="E46" t="s">
         <v>25</v>
@@ -5926,7 +6058,7 @@
         <v>35</v>
       </c>
       <c r="G46" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H46" t="s">
         <v>216</v>
@@ -5937,10 +6069,10 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>381</v>
+        <v>425</v>
       </c>
       <c r="D47" t="s">
-        <v>382</v>
+        <v>426</v>
       </c>
       <c r="E47" t="s">
         <v>25</v>
@@ -5949,7 +6081,7 @@
         <v>35</v>
       </c>
       <c r="G47" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H47" t="s">
         <v>216</v>
@@ -5960,10 +6092,10 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>383</v>
+        <v>427</v>
       </c>
       <c r="D48" t="s">
-        <v>384</v>
+        <v>428</v>
       </c>
       <c r="E48" t="s">
         <v>25</v>
@@ -5972,7 +6104,7 @@
         <v>35</v>
       </c>
       <c r="G48" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H48" t="s">
         <v>216</v>
@@ -5983,10 +6115,10 @@
         <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>385</v>
+        <v>429</v>
       </c>
       <c r="D49" t="s">
-        <v>386</v>
+        <v>430</v>
       </c>
       <c r="E49" t="s">
         <v>25</v>
@@ -5995,7 +6127,7 @@
         <v>35</v>
       </c>
       <c r="G49" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H49" t="s">
         <v>216</v>
@@ -6006,10 +6138,10 @@
         <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>387</v>
+        <v>431</v>
       </c>
       <c r="D50" t="s">
-        <v>388</v>
+        <v>432</v>
       </c>
       <c r="E50" t="s">
         <v>25</v>
@@ -6018,7 +6150,7 @@
         <v>35</v>
       </c>
       <c r="G50" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H50" t="s">
         <v>216</v>
@@ -6029,10 +6161,10 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>389</v>
+        <v>433</v>
       </c>
       <c r="D51" t="s">
-        <v>390</v>
+        <v>434</v>
       </c>
       <c r="E51" t="s">
         <v>25</v>
@@ -6041,7 +6173,7 @@
         <v>35</v>
       </c>
       <c r="G51" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H51" t="s">
         <v>216</v>
@@ -6052,10 +6184,10 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>391</v>
+        <v>435</v>
       </c>
       <c r="D52" t="s">
-        <v>392</v>
+        <v>436</v>
       </c>
       <c r="E52" t="s">
         <v>25</v>
@@ -6064,7 +6196,7 @@
         <v>35</v>
       </c>
       <c r="G52" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H52" t="s">
         <v>216</v>
@@ -6075,10 +6207,10 @@
         <v>17</v>
       </c>
       <c r="C53" t="s">
-        <v>393</v>
+        <v>437</v>
       </c>
       <c r="D53" t="s">
-        <v>394</v>
+        <v>438</v>
       </c>
       <c r="E53" t="s">
         <v>25</v>
@@ -6087,7 +6219,7 @@
         <v>35</v>
       </c>
       <c r="G53" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H53" t="s">
         <v>216</v>
@@ -6098,10 +6230,10 @@
         <v>17</v>
       </c>
       <c r="C54" t="s">
-        <v>395</v>
+        <v>439</v>
       </c>
       <c r="D54" t="s">
-        <v>396</v>
+        <v>440</v>
       </c>
       <c r="E54" t="s">
         <v>25</v>
@@ -6110,7 +6242,7 @@
         <v>35</v>
       </c>
       <c r="G54" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H54" t="s">
         <v>216</v>
@@ -6121,10 +6253,10 @@
         <v>17</v>
       </c>
       <c r="C55" t="s">
-        <v>397</v>
+        <v>441</v>
       </c>
       <c r="D55" t="s">
-        <v>398</v>
+        <v>442</v>
       </c>
       <c r="E55" t="s">
         <v>25</v>
@@ -6133,7 +6265,7 @@
         <v>35</v>
       </c>
       <c r="G55" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H55" t="s">
         <v>216</v>
@@ -6144,10 +6276,10 @@
         <v>17</v>
       </c>
       <c r="C56" t="s">
-        <v>399</v>
+        <v>443</v>
       </c>
       <c r="D56" t="s">
-        <v>400</v>
+        <v>444</v>
       </c>
       <c r="E56" t="s">
         <v>25</v>
@@ -6156,7 +6288,7 @@
         <v>35</v>
       </c>
       <c r="G56" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H56" t="s">
         <v>216</v>
@@ -6167,10 +6299,10 @@
         <v>17</v>
       </c>
       <c r="C57" t="s">
-        <v>401</v>
+        <v>445</v>
       </c>
       <c r="D57" t="s">
-        <v>402</v>
+        <v>446</v>
       </c>
       <c r="E57" t="s">
         <v>25</v>
@@ -6179,7 +6311,7 @@
         <v>35</v>
       </c>
       <c r="G57" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H57" t="s">
         <v>216</v>
@@ -6190,10 +6322,10 @@
         <v>17</v>
       </c>
       <c r="C58" t="s">
-        <v>403</v>
+        <v>447</v>
       </c>
       <c r="D58" t="s">
-        <v>404</v>
+        <v>448</v>
       </c>
       <c r="E58" t="s">
         <v>25</v>
@@ -6202,7 +6334,7 @@
         <v>35</v>
       </c>
       <c r="G58" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H58" t="s">
         <v>216</v>
@@ -6213,10 +6345,10 @@
         <v>17</v>
       </c>
       <c r="C59" t="s">
-        <v>405</v>
+        <v>449</v>
       </c>
       <c r="D59" t="s">
-        <v>406</v>
+        <v>450</v>
       </c>
       <c r="E59" t="s">
         <v>25</v>
@@ -6225,7 +6357,7 @@
         <v>35</v>
       </c>
       <c r="G59" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H59" t="s">
         <v>216</v>
@@ -6236,10 +6368,10 @@
         <v>17</v>
       </c>
       <c r="C60" t="s">
-        <v>407</v>
+        <v>451</v>
       </c>
       <c r="D60" t="s">
-        <v>408</v>
+        <v>452</v>
       </c>
       <c r="E60" t="s">
         <v>25</v>
@@ -6248,7 +6380,7 @@
         <v>35</v>
       </c>
       <c r="G60" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H60" t="s">
         <v>216</v>
@@ -6259,10 +6391,10 @@
         <v>17</v>
       </c>
       <c r="C61" t="s">
-        <v>409</v>
+        <v>453</v>
       </c>
       <c r="D61" t="s">
-        <v>410</v>
+        <v>454</v>
       </c>
       <c r="E61" t="s">
         <v>25</v>
@@ -6271,7 +6403,7 @@
         <v>35</v>
       </c>
       <c r="G61" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H61" t="s">
         <v>216</v>
@@ -6282,10 +6414,10 @@
         <v>17</v>
       </c>
       <c r="C62" t="s">
-        <v>411</v>
+        <v>455</v>
       </c>
       <c r="D62" t="s">
-        <v>412</v>
+        <v>456</v>
       </c>
       <c r="E62" t="s">
         <v>25</v>
@@ -6294,7 +6426,7 @@
         <v>35</v>
       </c>
       <c r="G62" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H62" t="s">
         <v>216</v>
@@ -6305,10 +6437,10 @@
         <v>17</v>
       </c>
       <c r="C63" t="s">
-        <v>413</v>
+        <v>457</v>
       </c>
       <c r="D63" t="s">
-        <v>414</v>
+        <v>458</v>
       </c>
       <c r="E63" t="s">
         <v>25</v>
@@ -6317,7 +6449,7 @@
         <v>35</v>
       </c>
       <c r="G63" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H63" t="s">
         <v>216</v>
@@ -6328,10 +6460,10 @@
         <v>17</v>
       </c>
       <c r="C64" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="D64" t="s">
-        <v>416</v>
+        <v>460</v>
       </c>
       <c r="E64" t="s">
         <v>25</v>
@@ -6340,7 +6472,7 @@
         <v>35</v>
       </c>
       <c r="G64" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H64" t="s">
         <v>216</v>
@@ -6351,10 +6483,10 @@
         <v>17</v>
       </c>
       <c r="C65" t="s">
-        <v>417</v>
+        <v>461</v>
       </c>
       <c r="D65" t="s">
-        <v>418</v>
+        <v>462</v>
       </c>
       <c r="E65" t="s">
         <v>25</v>
@@ -6363,7 +6495,7 @@
         <v>35</v>
       </c>
       <c r="G65" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H65" t="s">
         <v>216</v>
@@ -6374,10 +6506,10 @@
         <v>17</v>
       </c>
       <c r="C66" t="s">
-        <v>419</v>
+        <v>463</v>
       </c>
       <c r="D66" t="s">
-        <v>420</v>
+        <v>464</v>
       </c>
       <c r="E66" t="s">
         <v>25</v>
@@ -6386,7 +6518,7 @@
         <v>35</v>
       </c>
       <c r="G66" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H66" t="s">
         <v>216</v>
@@ -6397,10 +6529,10 @@
         <v>17</v>
       </c>
       <c r="C67" t="s">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="D67" t="s">
-        <v>422</v>
+        <v>466</v>
       </c>
       <c r="E67" t="s">
         <v>25</v>
@@ -6409,7 +6541,7 @@
         <v>35</v>
       </c>
       <c r="G67" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H67" t="s">
         <v>216</v>
@@ -6420,10 +6552,10 @@
         <v>17</v>
       </c>
       <c r="C68" t="s">
-        <v>423</v>
+        <v>467</v>
       </c>
       <c r="D68" t="s">
-        <v>424</v>
+        <v>468</v>
       </c>
       <c r="E68" t="s">
         <v>25</v>
@@ -6432,7 +6564,7 @@
         <v>35</v>
       </c>
       <c r="G68" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H68" t="s">
         <v>216</v>
@@ -6443,10 +6575,10 @@
         <v>17</v>
       </c>
       <c r="C69" t="s">
-        <v>425</v>
+        <v>469</v>
       </c>
       <c r="D69" t="s">
-        <v>426</v>
+        <v>470</v>
       </c>
       <c r="E69" t="s">
         <v>25</v>
@@ -6455,7 +6587,7 @@
         <v>35</v>
       </c>
       <c r="G69" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H69" t="s">
         <v>216</v>
@@ -6466,10 +6598,10 @@
         <v>17</v>
       </c>
       <c r="C70" t="s">
-        <v>427</v>
+        <v>471</v>
       </c>
       <c r="D70" t="s">
-        <v>428</v>
+        <v>472</v>
       </c>
       <c r="E70" t="s">
         <v>25</v>
@@ -6478,7 +6610,7 @@
         <v>35</v>
       </c>
       <c r="G70" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H70" t="s">
         <v>216</v>
@@ -6489,10 +6621,10 @@
         <v>17</v>
       </c>
       <c r="C71" t="s">
-        <v>429</v>
+        <v>473</v>
       </c>
       <c r="D71" t="s">
-        <v>430</v>
+        <v>474</v>
       </c>
       <c r="E71" t="s">
         <v>25</v>
@@ -6501,7 +6633,7 @@
         <v>35</v>
       </c>
       <c r="G71" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H71" t="s">
         <v>216</v>
@@ -6512,10 +6644,10 @@
         <v>17</v>
       </c>
       <c r="C72" t="s">
-        <v>431</v>
+        <v>475</v>
       </c>
       <c r="D72" t="s">
-        <v>432</v>
+        <v>476</v>
       </c>
       <c r="E72" t="s">
         <v>25</v>
@@ -6524,7 +6656,7 @@
         <v>35</v>
       </c>
       <c r="G72" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H72" t="s">
         <v>216</v>
@@ -6535,10 +6667,10 @@
         <v>17</v>
       </c>
       <c r="C73" t="s">
-        <v>433</v>
+        <v>477</v>
       </c>
       <c r="D73" t="s">
-        <v>434</v>
+        <v>478</v>
       </c>
       <c r="E73" t="s">
         <v>25</v>
@@ -6547,7 +6679,7 @@
         <v>35</v>
       </c>
       <c r="G73" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H73" t="s">
         <v>216</v>
@@ -6558,10 +6690,10 @@
         <v>17</v>
       </c>
       <c r="C74" t="s">
-        <v>435</v>
+        <v>479</v>
       </c>
       <c r="D74" t="s">
-        <v>436</v>
+        <v>480</v>
       </c>
       <c r="E74" t="s">
         <v>25</v>
@@ -6570,7 +6702,7 @@
         <v>35</v>
       </c>
       <c r="G74" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H74" t="s">
         <v>216</v>
@@ -6581,10 +6713,10 @@
         <v>17</v>
       </c>
       <c r="C75" t="s">
-        <v>437</v>
+        <v>481</v>
       </c>
       <c r="D75" t="s">
-        <v>438</v>
+        <v>482</v>
       </c>
       <c r="E75" t="s">
         <v>25</v>
@@ -6593,7 +6725,7 @@
         <v>35</v>
       </c>
       <c r="G75" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H75" t="s">
         <v>216</v>
@@ -6604,10 +6736,10 @@
         <v>17</v>
       </c>
       <c r="C76" t="s">
-        <v>439</v>
+        <v>483</v>
       </c>
       <c r="D76" t="s">
-        <v>440</v>
+        <v>484</v>
       </c>
       <c r="E76" t="s">
         <v>25</v>
@@ -6616,7 +6748,7 @@
         <v>35</v>
       </c>
       <c r="G76" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H76" t="s">
         <v>216</v>
@@ -6627,10 +6759,10 @@
         <v>17</v>
       </c>
       <c r="C77" t="s">
-        <v>441</v>
+        <v>485</v>
       </c>
       <c r="D77" t="s">
-        <v>442</v>
+        <v>486</v>
       </c>
       <c r="E77" t="s">
         <v>25</v>
@@ -6639,7 +6771,7 @@
         <v>35</v>
       </c>
       <c r="G77" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H77" t="s">
         <v>216</v>
@@ -6650,10 +6782,10 @@
         <v>17</v>
       </c>
       <c r="C78" t="s">
-        <v>443</v>
+        <v>487</v>
       </c>
       <c r="D78" t="s">
-        <v>444</v>
+        <v>488</v>
       </c>
       <c r="E78" t="s">
         <v>25</v>
@@ -6662,7 +6794,7 @@
         <v>35</v>
       </c>
       <c r="G78" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H78" t="s">
         <v>216</v>
@@ -6673,10 +6805,10 @@
         <v>17</v>
       </c>
       <c r="C79" t="s">
-        <v>445</v>
+        <v>489</v>
       </c>
       <c r="D79" t="s">
-        <v>446</v>
+        <v>490</v>
       </c>
       <c r="E79" t="s">
         <v>25</v>
@@ -6685,7 +6817,7 @@
         <v>35</v>
       </c>
       <c r="G79" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H79" t="s">
         <v>216</v>
@@ -6696,10 +6828,10 @@
         <v>17</v>
       </c>
       <c r="C80" t="s">
-        <v>447</v>
+        <v>491</v>
       </c>
       <c r="D80" t="s">
-        <v>448</v>
+        <v>492</v>
       </c>
       <c r="E80" t="s">
         <v>25</v>
@@ -6708,7 +6840,7 @@
         <v>35</v>
       </c>
       <c r="G80" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H80" t="s">
         <v>216</v>
@@ -6719,10 +6851,10 @@
         <v>17</v>
       </c>
       <c r="C81" t="s">
-        <v>449</v>
+        <v>493</v>
       </c>
       <c r="D81" t="s">
-        <v>450</v>
+        <v>494</v>
       </c>
       <c r="E81" t="s">
         <v>25</v>
@@ -6731,7 +6863,7 @@
         <v>35</v>
       </c>
       <c r="G81" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H81" t="s">
         <v>216</v>
@@ -6742,10 +6874,10 @@
         <v>17</v>
       </c>
       <c r="C82" t="s">
-        <v>451</v>
+        <v>495</v>
       </c>
       <c r="D82" t="s">
-        <v>452</v>
+        <v>496</v>
       </c>
       <c r="E82" t="s">
         <v>25</v>
@@ -6754,7 +6886,7 @@
         <v>35</v>
       </c>
       <c r="G82" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H82" t="s">
         <v>216</v>
@@ -6765,10 +6897,10 @@
         <v>17</v>
       </c>
       <c r="C83" t="s">
-        <v>453</v>
+        <v>497</v>
       </c>
       <c r="D83" t="s">
-        <v>454</v>
+        <v>498</v>
       </c>
       <c r="E83" t="s">
         <v>25</v>
@@ -6777,7 +6909,7 @@
         <v>35</v>
       </c>
       <c r="G83" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H83" t="s">
         <v>216</v>
@@ -6788,10 +6920,10 @@
         <v>17</v>
       </c>
       <c r="C84" t="s">
-        <v>455</v>
+        <v>499</v>
       </c>
       <c r="D84" t="s">
-        <v>456</v>
+        <v>500</v>
       </c>
       <c r="E84" t="s">
         <v>25</v>
@@ -6800,7 +6932,7 @@
         <v>35</v>
       </c>
       <c r="G84" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H84" t="s">
         <v>216</v>
@@ -6811,10 +6943,10 @@
         <v>17</v>
       </c>
       <c r="C85" t="s">
-        <v>457</v>
+        <v>501</v>
       </c>
       <c r="D85" t="s">
-        <v>458</v>
+        <v>502</v>
       </c>
       <c r="E85" t="s">
         <v>25</v>
@@ -6823,7 +6955,7 @@
         <v>35</v>
       </c>
       <c r="G85" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H85" t="s">
         <v>216</v>
@@ -6834,10 +6966,10 @@
         <v>17</v>
       </c>
       <c r="C86" t="s">
-        <v>459</v>
+        <v>503</v>
       </c>
       <c r="D86" t="s">
-        <v>460</v>
+        <v>504</v>
       </c>
       <c r="E86" t="s">
         <v>25</v>
@@ -6846,7 +6978,7 @@
         <v>35</v>
       </c>
       <c r="G86" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H86" t="s">
         <v>216</v>
@@ -6857,10 +6989,10 @@
         <v>17</v>
       </c>
       <c r="C87" t="s">
-        <v>461</v>
+        <v>505</v>
       </c>
       <c r="D87" t="s">
-        <v>462</v>
+        <v>506</v>
       </c>
       <c r="E87" t="s">
         <v>25</v>
@@ -6869,7 +7001,7 @@
         <v>35</v>
       </c>
       <c r="G87" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H87" t="s">
         <v>216</v>
@@ -6880,10 +7012,10 @@
         <v>17</v>
       </c>
       <c r="C88" t="s">
-        <v>463</v>
+        <v>507</v>
       </c>
       <c r="D88" t="s">
-        <v>464</v>
+        <v>508</v>
       </c>
       <c r="E88" t="s">
         <v>25</v>
@@ -6892,7 +7024,7 @@
         <v>35</v>
       </c>
       <c r="G88" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H88" t="s">
         <v>216</v>
@@ -6903,10 +7035,10 @@
         <v>17</v>
       </c>
       <c r="C89" t="s">
-        <v>465</v>
+        <v>509</v>
       </c>
       <c r="D89" t="s">
-        <v>466</v>
+        <v>510</v>
       </c>
       <c r="E89" t="s">
         <v>25</v>
@@ -6915,7 +7047,7 @@
         <v>35</v>
       </c>
       <c r="G89" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H89" t="s">
         <v>216</v>
@@ -6926,10 +7058,10 @@
         <v>17</v>
       </c>
       <c r="C90" t="s">
-        <v>467</v>
+        <v>511</v>
       </c>
       <c r="D90" t="s">
-        <v>468</v>
+        <v>512</v>
       </c>
       <c r="E90" t="s">
         <v>25</v>
@@ -6938,7 +7070,7 @@
         <v>35</v>
       </c>
       <c r="G90" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H90" t="s">
         <v>216</v>
@@ -6949,10 +7081,10 @@
         <v>17</v>
       </c>
       <c r="C91" t="s">
-        <v>469</v>
+        <v>513</v>
       </c>
       <c r="D91" t="s">
-        <v>470</v>
+        <v>514</v>
       </c>
       <c r="E91" t="s">
         <v>25</v>
@@ -6961,7 +7093,7 @@
         <v>35</v>
       </c>
       <c r="G91" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H91" t="s">
         <v>216</v>
@@ -6972,10 +7104,10 @@
         <v>17</v>
       </c>
       <c r="C92" t="s">
-        <v>471</v>
+        <v>515</v>
       </c>
       <c r="D92" t="s">
-        <v>472</v>
+        <v>516</v>
       </c>
       <c r="E92" t="s">
         <v>25</v>
@@ -6984,7 +7116,7 @@
         <v>35</v>
       </c>
       <c r="G92" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H92" t="s">
         <v>216</v>
@@ -6995,10 +7127,10 @@
         <v>17</v>
       </c>
       <c r="C93" t="s">
-        <v>473</v>
+        <v>517</v>
       </c>
       <c r="D93" t="s">
-        <v>474</v>
+        <v>518</v>
       </c>
       <c r="E93" t="s">
         <v>25</v>
@@ -7007,7 +7139,7 @@
         <v>35</v>
       </c>
       <c r="G93" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H93" t="s">
         <v>216</v>
@@ -7018,10 +7150,10 @@
         <v>17</v>
       </c>
       <c r="C94" t="s">
-        <v>475</v>
+        <v>519</v>
       </c>
       <c r="D94" t="s">
-        <v>476</v>
+        <v>520</v>
       </c>
       <c r="E94" t="s">
         <v>25</v>
@@ -7030,7 +7162,7 @@
         <v>35</v>
       </c>
       <c r="G94" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H94" t="s">
         <v>216</v>
@@ -7041,10 +7173,10 @@
         <v>17</v>
       </c>
       <c r="C95" t="s">
-        <v>477</v>
+        <v>521</v>
       </c>
       <c r="D95" t="s">
-        <v>478</v>
+        <v>522</v>
       </c>
       <c r="E95" t="s">
         <v>25</v>
@@ -7053,7 +7185,7 @@
         <v>35</v>
       </c>
       <c r="G95" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H95" t="s">
         <v>216</v>
@@ -7064,10 +7196,10 @@
         <v>17</v>
       </c>
       <c r="C96" t="s">
-        <v>479</v>
+        <v>523</v>
       </c>
       <c r="D96" t="s">
-        <v>480</v>
+        <v>524</v>
       </c>
       <c r="E96" t="s">
         <v>25</v>
@@ -7076,7 +7208,7 @@
         <v>35</v>
       </c>
       <c r="G96" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H96" t="s">
         <v>216</v>
@@ -7087,10 +7219,10 @@
         <v>17</v>
       </c>
       <c r="C97" t="s">
-        <v>481</v>
+        <v>525</v>
       </c>
       <c r="D97" t="s">
-        <v>482</v>
+        <v>526</v>
       </c>
       <c r="E97" t="s">
         <v>25</v>
@@ -7099,7 +7231,7 @@
         <v>35</v>
       </c>
       <c r="G97" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H97" t="s">
         <v>216</v>
@@ -7110,10 +7242,10 @@
         <v>17</v>
       </c>
       <c r="C98" t="s">
-        <v>483</v>
+        <v>527</v>
       </c>
       <c r="D98" t="s">
-        <v>484</v>
+        <v>528</v>
       </c>
       <c r="E98" t="s">
         <v>25</v>
@@ -7122,7 +7254,7 @@
         <v>35</v>
       </c>
       <c r="G98" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H98" t="s">
         <v>216</v>
@@ -7133,10 +7265,10 @@
         <v>17</v>
       </c>
       <c r="C99" t="s">
-        <v>485</v>
+        <v>529</v>
       </c>
       <c r="D99" t="s">
-        <v>486</v>
+        <v>530</v>
       </c>
       <c r="E99" t="s">
         <v>25</v>
@@ -7145,7 +7277,7 @@
         <v>35</v>
       </c>
       <c r="G99" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H99" t="s">
         <v>216</v>
@@ -7156,10 +7288,10 @@
         <v>17</v>
       </c>
       <c r="C100" t="s">
-        <v>487</v>
+        <v>531</v>
       </c>
       <c r="D100" t="s">
-        <v>488</v>
+        <v>532</v>
       </c>
       <c r="E100" t="s">
         <v>25</v>
@@ -7168,7 +7300,7 @@
         <v>35</v>
       </c>
       <c r="G100" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H100" t="s">
         <v>216</v>
@@ -7179,10 +7311,10 @@
         <v>17</v>
       </c>
       <c r="C101" t="s">
-        <v>489</v>
+        <v>533</v>
       </c>
       <c r="D101" t="s">
-        <v>490</v>
+        <v>534</v>
       </c>
       <c r="E101" t="s">
         <v>25</v>
@@ -7191,7 +7323,7 @@
         <v>35</v>
       </c>
       <c r="G101" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H101" t="s">
         <v>216</v>
@@ -7202,10 +7334,10 @@
         <v>17</v>
       </c>
       <c r="C102" t="s">
-        <v>491</v>
+        <v>535</v>
       </c>
       <c r="D102" t="s">
-        <v>492</v>
+        <v>536</v>
       </c>
       <c r="E102" t="s">
         <v>25</v>
@@ -7214,7 +7346,7 @@
         <v>35</v>
       </c>
       <c r="G102" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H102" t="s">
         <v>216</v>
@@ -7225,10 +7357,10 @@
         <v>17</v>
       </c>
       <c r="C103" t="s">
-        <v>493</v>
+        <v>537</v>
       </c>
       <c r="D103" t="s">
-        <v>494</v>
+        <v>538</v>
       </c>
       <c r="E103" t="s">
         <v>25</v>
@@ -7237,7 +7369,7 @@
         <v>35</v>
       </c>
       <c r="G103" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H103" t="s">
         <v>216</v>
@@ -7248,10 +7380,10 @@
         <v>17</v>
       </c>
       <c r="C104" t="s">
-        <v>495</v>
+        <v>539</v>
       </c>
       <c r="D104" t="s">
-        <v>496</v>
+        <v>540</v>
       </c>
       <c r="E104" t="s">
         <v>25</v>
@@ -7260,7 +7392,7 @@
         <v>35</v>
       </c>
       <c r="G104" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H104" t="s">
         <v>216</v>
@@ -7271,10 +7403,10 @@
         <v>17</v>
       </c>
       <c r="C105" t="s">
-        <v>497</v>
+        <v>541</v>
       </c>
       <c r="D105" t="s">
-        <v>498</v>
+        <v>542</v>
       </c>
       <c r="E105" t="s">
         <v>25</v>
@@ -7283,7 +7415,7 @@
         <v>35</v>
       </c>
       <c r="G105" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H105" t="s">
         <v>216</v>
@@ -7294,10 +7426,10 @@
         <v>17</v>
       </c>
       <c r="C106" t="s">
-        <v>499</v>
+        <v>543</v>
       </c>
       <c r="D106" t="s">
-        <v>500</v>
+        <v>544</v>
       </c>
       <c r="E106" t="s">
         <v>25</v>
@@ -7306,7 +7438,7 @@
         <v>35</v>
       </c>
       <c r="G106" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H106" t="s">
         <v>216</v>
@@ -7317,10 +7449,10 @@
         <v>17</v>
       </c>
       <c r="C107" t="s">
-        <v>501</v>
+        <v>545</v>
       </c>
       <c r="D107" t="s">
-        <v>502</v>
+        <v>546</v>
       </c>
       <c r="E107" t="s">
         <v>25</v>
@@ -7329,7 +7461,7 @@
         <v>35</v>
       </c>
       <c r="G107" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H107" t="s">
         <v>216</v>
@@ -7340,10 +7472,10 @@
         <v>17</v>
       </c>
       <c r="C108" t="s">
-        <v>503</v>
+        <v>547</v>
       </c>
       <c r="D108" t="s">
-        <v>504</v>
+        <v>548</v>
       </c>
       <c r="E108" t="s">
         <v>25</v>
@@ -7352,7 +7484,7 @@
         <v>35</v>
       </c>
       <c r="G108" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H108" t="s">
         <v>216</v>
@@ -7363,10 +7495,10 @@
         <v>17</v>
       </c>
       <c r="C109" t="s">
-        <v>505</v>
+        <v>549</v>
       </c>
       <c r="D109" t="s">
-        <v>506</v>
+        <v>550</v>
       </c>
       <c r="E109" t="s">
         <v>25</v>
@@ -7375,7 +7507,7 @@
         <v>35</v>
       </c>
       <c r="G109" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H109" t="s">
         <v>216</v>
@@ -7386,10 +7518,10 @@
         <v>17</v>
       </c>
       <c r="C110" t="s">
-        <v>507</v>
+        <v>551</v>
       </c>
       <c r="D110" t="s">
-        <v>508</v>
+        <v>552</v>
       </c>
       <c r="E110" t="s">
         <v>25</v>
@@ -7398,7 +7530,7 @@
         <v>35</v>
       </c>
       <c r="G110" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H110" t="s">
         <v>216</v>
@@ -7409,10 +7541,10 @@
         <v>17</v>
       </c>
       <c r="C111" t="s">
-        <v>509</v>
+        <v>553</v>
       </c>
       <c r="D111" t="s">
-        <v>510</v>
+        <v>554</v>
       </c>
       <c r="E111" t="s">
         <v>25</v>
@@ -7421,7 +7553,7 @@
         <v>35</v>
       </c>
       <c r="G111" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H111" t="s">
         <v>216</v>
@@ -7432,10 +7564,10 @@
         <v>17</v>
       </c>
       <c r="C112" t="s">
-        <v>511</v>
+        <v>555</v>
       </c>
       <c r="D112" t="s">
-        <v>512</v>
+        <v>556</v>
       </c>
       <c r="E112" t="s">
         <v>25</v>
@@ -7444,7 +7576,7 @@
         <v>35</v>
       </c>
       <c r="G112" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H112" t="s">
         <v>216</v>
@@ -7455,10 +7587,10 @@
         <v>17</v>
       </c>
       <c r="C113" t="s">
-        <v>513</v>
+        <v>557</v>
       </c>
       <c r="D113" t="s">
-        <v>514</v>
+        <v>558</v>
       </c>
       <c r="E113" t="s">
         <v>25</v>
@@ -7467,7 +7599,7 @@
         <v>35</v>
       </c>
       <c r="G113" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H113" t="s">
         <v>216</v>
@@ -7478,10 +7610,10 @@
         <v>17</v>
       </c>
       <c r="C114" t="s">
-        <v>515</v>
+        <v>559</v>
       </c>
       <c r="D114" t="s">
-        <v>516</v>
+        <v>560</v>
       </c>
       <c r="E114" t="s">
         <v>25</v>
@@ -7490,7 +7622,7 @@
         <v>35</v>
       </c>
       <c r="G114" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H114" t="s">
         <v>216</v>
@@ -7501,10 +7633,10 @@
         <v>17</v>
       </c>
       <c r="C115" t="s">
-        <v>517</v>
+        <v>561</v>
       </c>
       <c r="D115" t="s">
-        <v>518</v>
+        <v>562</v>
       </c>
       <c r="E115" t="s">
         <v>25</v>
@@ -7513,7 +7645,7 @@
         <v>35</v>
       </c>
       <c r="G115" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H115" t="s">
         <v>216</v>
@@ -7524,10 +7656,10 @@
         <v>17</v>
       </c>
       <c r="C116" t="s">
-        <v>519</v>
+        <v>563</v>
       </c>
       <c r="D116" t="s">
-        <v>520</v>
+        <v>564</v>
       </c>
       <c r="E116" t="s">
         <v>25</v>
@@ -7536,7 +7668,7 @@
         <v>35</v>
       </c>
       <c r="G116" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H116" t="s">
         <v>216</v>
@@ -7547,10 +7679,10 @@
         <v>17</v>
       </c>
       <c r="C117" t="s">
-        <v>521</v>
+        <v>565</v>
       </c>
       <c r="D117" t="s">
-        <v>522</v>
+        <v>566</v>
       </c>
       <c r="E117" t="s">
         <v>25</v>
@@ -7559,7 +7691,7 @@
         <v>35</v>
       </c>
       <c r="G117" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H117" t="s">
         <v>216</v>
@@ -7570,10 +7702,10 @@
         <v>17</v>
       </c>
       <c r="C118" t="s">
-        <v>523</v>
+        <v>567</v>
       </c>
       <c r="D118" t="s">
-        <v>524</v>
+        <v>568</v>
       </c>
       <c r="E118" t="s">
         <v>25</v>
@@ -7582,7 +7714,7 @@
         <v>35</v>
       </c>
       <c r="G118" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H118" t="s">
         <v>216</v>
@@ -7593,10 +7725,10 @@
         <v>17</v>
       </c>
       <c r="C119" t="s">
-        <v>525</v>
+        <v>569</v>
       </c>
       <c r="D119" t="s">
-        <v>526</v>
+        <v>570</v>
       </c>
       <c r="E119" t="s">
         <v>25</v>
@@ -7605,7 +7737,7 @@
         <v>35</v>
       </c>
       <c r="G119" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H119" t="s">
         <v>216</v>
@@ -7616,10 +7748,10 @@
         <v>17</v>
       </c>
       <c r="C120" t="s">
-        <v>527</v>
+        <v>571</v>
       </c>
       <c r="D120" t="s">
-        <v>528</v>
+        <v>572</v>
       </c>
       <c r="E120" t="s">
         <v>25</v>
@@ -7628,7 +7760,7 @@
         <v>35</v>
       </c>
       <c r="G120" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H120" t="s">
         <v>216</v>
@@ -7639,10 +7771,10 @@
         <v>17</v>
       </c>
       <c r="C121" t="s">
-        <v>529</v>
+        <v>573</v>
       </c>
       <c r="D121" t="s">
-        <v>530</v>
+        <v>574</v>
       </c>
       <c r="E121" t="s">
         <v>25</v>
@@ -7651,7 +7783,7 @@
         <v>35</v>
       </c>
       <c r="G121" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H121" t="s">
         <v>216</v>
@@ -7662,10 +7794,10 @@
         <v>17</v>
       </c>
       <c r="C122" t="s">
-        <v>531</v>
+        <v>575</v>
       </c>
       <c r="D122" t="s">
-        <v>532</v>
+        <v>576</v>
       </c>
       <c r="E122" t="s">
         <v>25</v>
@@ -7674,7 +7806,7 @@
         <v>35</v>
       </c>
       <c r="G122" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H122" t="s">
         <v>216</v>
@@ -7685,10 +7817,10 @@
         <v>17</v>
       </c>
       <c r="C123" t="s">
-        <v>533</v>
+        <v>577</v>
       </c>
       <c r="D123" t="s">
-        <v>534</v>
+        <v>578</v>
       </c>
       <c r="E123" t="s">
         <v>25</v>
@@ -7697,7 +7829,7 @@
         <v>35</v>
       </c>
       <c r="G123" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H123" t="s">
         <v>216</v>
@@ -7708,10 +7840,10 @@
         <v>17</v>
       </c>
       <c r="C124" t="s">
-        <v>535</v>
+        <v>579</v>
       </c>
       <c r="D124" t="s">
-        <v>536</v>
+        <v>580</v>
       </c>
       <c r="E124" t="s">
         <v>25</v>
@@ -7720,7 +7852,7 @@
         <v>35</v>
       </c>
       <c r="G124" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H124" t="s">
         <v>216</v>
@@ -7731,10 +7863,10 @@
         <v>17</v>
       </c>
       <c r="C125" t="s">
-        <v>537</v>
+        <v>581</v>
       </c>
       <c r="D125" t="s">
-        <v>538</v>
+        <v>582</v>
       </c>
       <c r="E125" t="s">
         <v>25</v>
@@ -7743,7 +7875,7 @@
         <v>35</v>
       </c>
       <c r="G125" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H125" t="s">
         <v>216</v>
@@ -7754,10 +7886,10 @@
         <v>17</v>
       </c>
       <c r="C126" t="s">
-        <v>539</v>
+        <v>583</v>
       </c>
       <c r="D126" t="s">
-        <v>540</v>
+        <v>584</v>
       </c>
       <c r="E126" t="s">
         <v>25</v>
@@ -7766,7 +7898,7 @@
         <v>35</v>
       </c>
       <c r="G126" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H126" t="s">
         <v>216</v>
@@ -7777,10 +7909,10 @@
         <v>17</v>
       </c>
       <c r="C127" t="s">
-        <v>541</v>
+        <v>585</v>
       </c>
       <c r="D127" t="s">
-        <v>542</v>
+        <v>586</v>
       </c>
       <c r="E127" t="s">
         <v>25</v>
@@ -7789,7 +7921,7 @@
         <v>35</v>
       </c>
       <c r="G127" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H127" t="s">
         <v>216</v>
@@ -7800,10 +7932,10 @@
         <v>17</v>
       </c>
       <c r="C128" t="s">
-        <v>543</v>
+        <v>587</v>
       </c>
       <c r="D128" t="s">
-        <v>544</v>
+        <v>588</v>
       </c>
       <c r="E128" t="s">
         <v>25</v>
@@ -7812,7 +7944,7 @@
         <v>35</v>
       </c>
       <c r="G128" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H128" t="s">
         <v>216</v>
@@ -7823,10 +7955,10 @@
         <v>17</v>
       </c>
       <c r="C129" t="s">
-        <v>545</v>
+        <v>589</v>
       </c>
       <c r="D129" t="s">
-        <v>546</v>
+        <v>590</v>
       </c>
       <c r="E129" t="s">
         <v>25</v>
@@ -7835,7 +7967,7 @@
         <v>35</v>
       </c>
       <c r="G129" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H129" t="s">
         <v>216</v>
@@ -7846,10 +7978,10 @@
         <v>17</v>
       </c>
       <c r="C130" t="s">
-        <v>547</v>
+        <v>591</v>
       </c>
       <c r="D130" t="s">
-        <v>548</v>
+        <v>592</v>
       </c>
       <c r="E130" t="s">
         <v>25</v>
@@ -7858,7 +7990,7 @@
         <v>35</v>
       </c>
       <c r="G130" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H130" t="s">
         <v>216</v>
@@ -7869,10 +8001,10 @@
         <v>17</v>
       </c>
       <c r="C131" t="s">
-        <v>549</v>
+        <v>593</v>
       </c>
       <c r="D131" t="s">
-        <v>550</v>
+        <v>594</v>
       </c>
       <c r="E131" t="s">
         <v>25</v>
@@ -7881,7 +8013,7 @@
         <v>35</v>
       </c>
       <c r="G131" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H131" t="s">
         <v>216</v>
@@ -7892,10 +8024,10 @@
         <v>17</v>
       </c>
       <c r="C132" t="s">
-        <v>551</v>
+        <v>595</v>
       </c>
       <c r="D132" t="s">
-        <v>552</v>
+        <v>596</v>
       </c>
       <c r="E132" t="s">
         <v>25</v>
@@ -7904,7 +8036,7 @@
         <v>35</v>
       </c>
       <c r="G132" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H132" t="s">
         <v>216</v>
@@ -7915,10 +8047,10 @@
         <v>17</v>
       </c>
       <c r="C133" t="s">
-        <v>553</v>
+        <v>597</v>
       </c>
       <c r="D133" t="s">
-        <v>554</v>
+        <v>598</v>
       </c>
       <c r="E133" t="s">
         <v>25</v>
@@ -7927,7 +8059,7 @@
         <v>35</v>
       </c>
       <c r="G133" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H133" t="s">
         <v>216</v>
@@ -7938,10 +8070,10 @@
         <v>17</v>
       </c>
       <c r="C134" t="s">
-        <v>555</v>
+        <v>599</v>
       </c>
       <c r="D134" t="s">
-        <v>556</v>
+        <v>600</v>
       </c>
       <c r="E134" t="s">
         <v>25</v>
@@ -7950,7 +8082,7 @@
         <v>35</v>
       </c>
       <c r="G134" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H134" t="s">
         <v>216</v>
@@ -7961,10 +8093,10 @@
         <v>17</v>
       </c>
       <c r="C135" t="s">
-        <v>557</v>
+        <v>601</v>
       </c>
       <c r="D135" t="s">
-        <v>558</v>
+        <v>602</v>
       </c>
       <c r="E135" t="s">
         <v>25</v>
@@ -7973,7 +8105,7 @@
         <v>35</v>
       </c>
       <c r="G135" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H135" t="s">
         <v>216</v>
@@ -7984,10 +8116,10 @@
         <v>17</v>
       </c>
       <c r="C136" t="s">
-        <v>559</v>
+        <v>603</v>
       </c>
       <c r="D136" t="s">
-        <v>560</v>
+        <v>604</v>
       </c>
       <c r="E136" t="s">
         <v>25</v>
@@ -7996,7 +8128,7 @@
         <v>35</v>
       </c>
       <c r="G136" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H136" t="s">
         <v>216</v>
@@ -8007,10 +8139,10 @@
         <v>17</v>
       </c>
       <c r="C137" t="s">
-        <v>561</v>
+        <v>605</v>
       </c>
       <c r="D137" t="s">
-        <v>562</v>
+        <v>606</v>
       </c>
       <c r="E137" t="s">
         <v>25</v>
@@ -8019,7 +8151,7 @@
         <v>35</v>
       </c>
       <c r="G137" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H137" t="s">
         <v>216</v>
@@ -8030,10 +8162,10 @@
         <v>17</v>
       </c>
       <c r="C138" t="s">
-        <v>563</v>
+        <v>607</v>
       </c>
       <c r="D138" t="s">
-        <v>564</v>
+        <v>608</v>
       </c>
       <c r="E138" t="s">
         <v>25</v>
@@ -8042,7 +8174,7 @@
         <v>35</v>
       </c>
       <c r="G138" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H138" t="s">
         <v>216</v>
@@ -8053,10 +8185,10 @@
         <v>17</v>
       </c>
       <c r="C139" t="s">
-        <v>565</v>
+        <v>609</v>
       </c>
       <c r="D139" t="s">
-        <v>566</v>
+        <v>610</v>
       </c>
       <c r="E139" t="s">
         <v>25</v>
@@ -8065,7 +8197,7 @@
         <v>35</v>
       </c>
       <c r="G139" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H139" t="s">
         <v>216</v>
@@ -8076,10 +8208,10 @@
         <v>17</v>
       </c>
       <c r="C140" t="s">
-        <v>567</v>
+        <v>611</v>
       </c>
       <c r="D140" t="s">
-        <v>568</v>
+        <v>612</v>
       </c>
       <c r="E140" t="s">
         <v>25</v>
@@ -8088,7 +8220,7 @@
         <v>35</v>
       </c>
       <c r="G140" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H140" t="s">
         <v>216</v>
@@ -8099,10 +8231,10 @@
         <v>17</v>
       </c>
       <c r="C141" t="s">
-        <v>569</v>
+        <v>613</v>
       </c>
       <c r="D141" t="s">
-        <v>570</v>
+        <v>614</v>
       </c>
       <c r="E141" t="s">
         <v>25</v>
@@ -8111,7 +8243,7 @@
         <v>35</v>
       </c>
       <c r="G141" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H141" t="s">
         <v>216</v>
@@ -8122,10 +8254,10 @@
         <v>17</v>
       </c>
       <c r="C142" t="s">
-        <v>571</v>
+        <v>615</v>
       </c>
       <c r="D142" t="s">
-        <v>572</v>
+        <v>616</v>
       </c>
       <c r="E142" t="s">
         <v>25</v>
@@ -8134,7 +8266,7 @@
         <v>35</v>
       </c>
       <c r="G142" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H142" t="s">
         <v>216</v>
@@ -8145,10 +8277,10 @@
         <v>17</v>
       </c>
       <c r="C143" t="s">
-        <v>573</v>
+        <v>617</v>
       </c>
       <c r="D143" t="s">
-        <v>574</v>
+        <v>618</v>
       </c>
       <c r="E143" t="s">
         <v>25</v>
@@ -8157,7 +8289,7 @@
         <v>35</v>
       </c>
       <c r="G143" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H143" t="s">
         <v>216</v>
@@ -8168,10 +8300,10 @@
         <v>17</v>
       </c>
       <c r="C144" t="s">
-        <v>575</v>
+        <v>619</v>
       </c>
       <c r="D144" t="s">
-        <v>576</v>
+        <v>620</v>
       </c>
       <c r="E144" t="s">
         <v>25</v>
@@ -8180,7 +8312,7 @@
         <v>35</v>
       </c>
       <c r="G144" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H144" t="s">
         <v>216</v>
@@ -8191,10 +8323,10 @@
         <v>17</v>
       </c>
       <c r="C145" t="s">
-        <v>577</v>
+        <v>621</v>
       </c>
       <c r="D145" t="s">
-        <v>578</v>
+        <v>622</v>
       </c>
       <c r="E145" t="s">
         <v>25</v>
@@ -8203,7 +8335,7 @@
         <v>35</v>
       </c>
       <c r="G145" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H145" t="s">
         <v>216</v>
@@ -8214,10 +8346,10 @@
         <v>17</v>
       </c>
       <c r="C146" t="s">
-        <v>579</v>
+        <v>623</v>
       </c>
       <c r="D146" t="s">
-        <v>580</v>
+        <v>624</v>
       </c>
       <c r="E146" t="s">
         <v>25</v>
@@ -8226,7 +8358,7 @@
         <v>35</v>
       </c>
       <c r="G146" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H146" t="s">
         <v>216</v>
@@ -8237,10 +8369,10 @@
         <v>17</v>
       </c>
       <c r="C147" t="s">
-        <v>581</v>
+        <v>625</v>
       </c>
       <c r="D147" t="s">
-        <v>582</v>
+        <v>626</v>
       </c>
       <c r="E147" t="s">
         <v>25</v>
@@ -8249,7 +8381,7 @@
         <v>35</v>
       </c>
       <c r="G147" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H147" t="s">
         <v>216</v>
@@ -8260,10 +8392,10 @@
         <v>17</v>
       </c>
       <c r="C148" t="s">
-        <v>583</v>
+        <v>627</v>
       </c>
       <c r="D148" t="s">
-        <v>584</v>
+        <v>628</v>
       </c>
       <c r="E148" t="s">
         <v>25</v>
@@ -8272,7 +8404,7 @@
         <v>35</v>
       </c>
       <c r="G148" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H148" t="s">
         <v>216</v>
@@ -8283,10 +8415,10 @@
         <v>17</v>
       </c>
       <c r="C149" t="s">
-        <v>585</v>
+        <v>629</v>
       </c>
       <c r="D149" t="s">
-        <v>586</v>
+        <v>630</v>
       </c>
       <c r="E149" t="s">
         <v>25</v>
@@ -8295,7 +8427,7 @@
         <v>35</v>
       </c>
       <c r="G149" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H149" t="s">
         <v>216</v>
@@ -8306,10 +8438,10 @@
         <v>17</v>
       </c>
       <c r="C150" t="s">
-        <v>587</v>
+        <v>631</v>
       </c>
       <c r="D150" t="s">
-        <v>588</v>
+        <v>632</v>
       </c>
       <c r="E150" t="s">
         <v>25</v>
@@ -8318,7 +8450,7 @@
         <v>35</v>
       </c>
       <c r="G150" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H150" t="s">
         <v>216</v>
@@ -8329,10 +8461,10 @@
         <v>17</v>
       </c>
       <c r="C151" t="s">
-        <v>589</v>
+        <v>633</v>
       </c>
       <c r="D151" t="s">
-        <v>590</v>
+        <v>634</v>
       </c>
       <c r="E151" t="s">
         <v>25</v>
@@ -8341,7 +8473,7 @@
         <v>35</v>
       </c>
       <c r="G151" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H151" t="s">
         <v>216</v>
@@ -8352,10 +8484,10 @@
         <v>17</v>
       </c>
       <c r="C152" t="s">
-        <v>591</v>
+        <v>635</v>
       </c>
       <c r="D152" t="s">
-        <v>592</v>
+        <v>636</v>
       </c>
       <c r="E152" t="s">
         <v>25</v>
@@ -8364,7 +8496,7 @@
         <v>35</v>
       </c>
       <c r="G152" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H152" t="s">
         <v>216</v>
@@ -8375,10 +8507,10 @@
         <v>17</v>
       </c>
       <c r="C153" t="s">
-        <v>593</v>
+        <v>637</v>
       </c>
       <c r="D153" t="s">
-        <v>594</v>
+        <v>638</v>
       </c>
       <c r="E153" t="s">
         <v>25</v>
@@ -8387,7 +8519,7 @@
         <v>35</v>
       </c>
       <c r="G153" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H153" t="s">
         <v>216</v>
@@ -8398,10 +8530,10 @@
         <v>17</v>
       </c>
       <c r="C154" t="s">
-        <v>595</v>
+        <v>639</v>
       </c>
       <c r="D154" t="s">
-        <v>596</v>
+        <v>640</v>
       </c>
       <c r="E154" t="s">
         <v>25</v>
@@ -8410,7 +8542,7 @@
         <v>35</v>
       </c>
       <c r="G154" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H154" t="s">
         <v>216</v>
@@ -8421,10 +8553,10 @@
         <v>17</v>
       </c>
       <c r="C155" t="s">
-        <v>597</v>
+        <v>641</v>
       </c>
       <c r="D155" t="s">
-        <v>598</v>
+        <v>642</v>
       </c>
       <c r="E155" t="s">
         <v>25</v>
@@ -8433,7 +8565,7 @@
         <v>35</v>
       </c>
       <c r="G155" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H155" t="s">
         <v>216</v>
@@ -8444,10 +8576,10 @@
         <v>17</v>
       </c>
       <c r="C156" t="s">
-        <v>599</v>
+        <v>643</v>
       </c>
       <c r="D156" t="s">
-        <v>600</v>
+        <v>644</v>
       </c>
       <c r="E156" t="s">
         <v>25</v>
@@ -8456,7 +8588,7 @@
         <v>35</v>
       </c>
       <c r="G156" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H156" t="s">
         <v>216</v>
@@ -8467,10 +8599,10 @@
         <v>17</v>
       </c>
       <c r="C157" t="s">
-        <v>601</v>
+        <v>645</v>
       </c>
       <c r="D157" t="s">
-        <v>602</v>
+        <v>646</v>
       </c>
       <c r="E157" t="s">
         <v>25</v>
@@ -8479,7 +8611,7 @@
         <v>35</v>
       </c>
       <c r="G157" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H157" t="s">
         <v>216</v>
@@ -8490,10 +8622,10 @@
         <v>17</v>
       </c>
       <c r="C158" t="s">
-        <v>603</v>
+        <v>647</v>
       </c>
       <c r="D158" t="s">
-        <v>604</v>
+        <v>648</v>
       </c>
       <c r="E158" t="s">
         <v>25</v>
@@ -8502,7 +8634,7 @@
         <v>35</v>
       </c>
       <c r="G158" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H158" t="s">
         <v>216</v>
@@ -8513,10 +8645,10 @@
         <v>17</v>
       </c>
       <c r="C159" t="s">
-        <v>605</v>
+        <v>649</v>
       </c>
       <c r="D159" t="s">
-        <v>606</v>
+        <v>650</v>
       </c>
       <c r="E159" t="s">
         <v>25</v>
@@ -8525,7 +8657,7 @@
         <v>35</v>
       </c>
       <c r="G159" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H159" t="s">
         <v>216</v>
@@ -8536,10 +8668,10 @@
         <v>17</v>
       </c>
       <c r="C160" t="s">
-        <v>607</v>
+        <v>651</v>
       </c>
       <c r="D160" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="E160" t="s">
         <v>25</v>
@@ -8548,7 +8680,7 @@
         <v>35</v>
       </c>
       <c r="G160" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H160" t="s">
         <v>216</v>
@@ -8559,10 +8691,10 @@
         <v>17</v>
       </c>
       <c r="C161" t="s">
-        <v>609</v>
+        <v>653</v>
       </c>
       <c r="D161" t="s">
-        <v>610</v>
+        <v>654</v>
       </c>
       <c r="E161" t="s">
         <v>25</v>
@@ -8571,7 +8703,7 @@
         <v>35</v>
       </c>
       <c r="G161" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H161" t="s">
         <v>216</v>
@@ -8582,10 +8714,10 @@
         <v>17</v>
       </c>
       <c r="C162" t="s">
-        <v>611</v>
+        <v>655</v>
       </c>
       <c r="D162" t="s">
-        <v>612</v>
+        <v>656</v>
       </c>
       <c r="E162" t="s">
         <v>25</v>
@@ -8594,7 +8726,7 @@
         <v>35</v>
       </c>
       <c r="G162" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H162" t="s">
         <v>216</v>
@@ -8605,10 +8737,10 @@
         <v>17</v>
       </c>
       <c r="C163" t="s">
-        <v>613</v>
+        <v>657</v>
       </c>
       <c r="D163" t="s">
-        <v>614</v>
+        <v>658</v>
       </c>
       <c r="E163" t="s">
         <v>25</v>
@@ -8617,7 +8749,7 @@
         <v>35</v>
       </c>
       <c r="G163" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H163" t="s">
         <v>216</v>
@@ -8628,10 +8760,10 @@
         <v>17</v>
       </c>
       <c r="C164" t="s">
-        <v>615</v>
+        <v>659</v>
       </c>
       <c r="D164" t="s">
-        <v>616</v>
+        <v>660</v>
       </c>
       <c r="E164" t="s">
         <v>25</v>
@@ -8640,7 +8772,7 @@
         <v>35</v>
       </c>
       <c r="G164" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H164" t="s">
         <v>216</v>
@@ -8651,10 +8783,10 @@
         <v>17</v>
       </c>
       <c r="C165" t="s">
-        <v>617</v>
+        <v>661</v>
       </c>
       <c r="D165" t="s">
-        <v>618</v>
+        <v>662</v>
       </c>
       <c r="E165" t="s">
         <v>25</v>
@@ -8663,7 +8795,7 @@
         <v>35</v>
       </c>
       <c r="G165" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H165" t="s">
         <v>216</v>
@@ -8674,10 +8806,10 @@
         <v>17</v>
       </c>
       <c r="C166" t="s">
-        <v>619</v>
+        <v>663</v>
       </c>
       <c r="D166" t="s">
-        <v>620</v>
+        <v>664</v>
       </c>
       <c r="E166" t="s">
         <v>25</v>
@@ -8686,7 +8818,7 @@
         <v>35</v>
       </c>
       <c r="G166" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H166" t="s">
         <v>216</v>
@@ -8697,10 +8829,10 @@
         <v>17</v>
       </c>
       <c r="C167" t="s">
-        <v>621</v>
+        <v>665</v>
       </c>
       <c r="D167" t="s">
-        <v>622</v>
+        <v>666</v>
       </c>
       <c r="E167" t="s">
         <v>25</v>
@@ -8709,7 +8841,7 @@
         <v>35</v>
       </c>
       <c r="G167" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H167" t="s">
         <v>216</v>
@@ -8720,10 +8852,10 @@
         <v>17</v>
       </c>
       <c r="C168" t="s">
-        <v>623</v>
+        <v>667</v>
       </c>
       <c r="D168" t="s">
-        <v>624</v>
+        <v>668</v>
       </c>
       <c r="E168" t="s">
         <v>25</v>
@@ -8732,7 +8864,7 @@
         <v>35</v>
       </c>
       <c r="G168" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H168" t="s">
         <v>216</v>
@@ -8743,10 +8875,10 @@
         <v>17</v>
       </c>
       <c r="C169" t="s">
-        <v>625</v>
+        <v>669</v>
       </c>
       <c r="D169" t="s">
-        <v>626</v>
+        <v>670</v>
       </c>
       <c r="E169" t="s">
         <v>25</v>
@@ -8755,7 +8887,7 @@
         <v>35</v>
       </c>
       <c r="G169" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H169" t="s">
         <v>216</v>
@@ -8766,10 +8898,10 @@
         <v>17</v>
       </c>
       <c r="C170" t="s">
-        <v>627</v>
+        <v>671</v>
       </c>
       <c r="D170" t="s">
-        <v>628</v>
+        <v>672</v>
       </c>
       <c r="E170" t="s">
         <v>25</v>
@@ -8778,7 +8910,7 @@
         <v>35</v>
       </c>
       <c r="G170" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H170" t="s">
         <v>216</v>
@@ -8789,10 +8921,10 @@
         <v>17</v>
       </c>
       <c r="C171" t="s">
-        <v>629</v>
+        <v>673</v>
       </c>
       <c r="D171" t="s">
-        <v>630</v>
+        <v>674</v>
       </c>
       <c r="E171" t="s">
         <v>25</v>
@@ -8801,7 +8933,7 @@
         <v>35</v>
       </c>
       <c r="G171" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H171" t="s">
         <v>216</v>
@@ -8812,10 +8944,10 @@
         <v>17</v>
       </c>
       <c r="C172" t="s">
-        <v>631</v>
+        <v>675</v>
       </c>
       <c r="D172" t="s">
-        <v>632</v>
+        <v>676</v>
       </c>
       <c r="E172" t="s">
         <v>25</v>
@@ -8824,7 +8956,7 @@
         <v>35</v>
       </c>
       <c r="G172" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H172" t="s">
         <v>216</v>
@@ -8835,10 +8967,10 @@
         <v>17</v>
       </c>
       <c r="C173" t="s">
-        <v>633</v>
+        <v>677</v>
       </c>
       <c r="D173" t="s">
-        <v>634</v>
+        <v>678</v>
       </c>
       <c r="E173" t="s">
         <v>25</v>
@@ -8847,7 +8979,7 @@
         <v>35</v>
       </c>
       <c r="G173" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H173" t="s">
         <v>216</v>
@@ -8858,10 +8990,10 @@
         <v>17</v>
       </c>
       <c r="C174" t="s">
-        <v>635</v>
+        <v>679</v>
       </c>
       <c r="D174" t="s">
-        <v>636</v>
+        <v>680</v>
       </c>
       <c r="E174" t="s">
         <v>25</v>
@@ -8870,7 +9002,7 @@
         <v>35</v>
       </c>
       <c r="G174" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H174" t="s">
         <v>216</v>
@@ -8881,10 +9013,10 @@
         <v>17</v>
       </c>
       <c r="C175" t="s">
-        <v>637</v>
+        <v>681</v>
       </c>
       <c r="D175" t="s">
-        <v>638</v>
+        <v>682</v>
       </c>
       <c r="E175" t="s">
         <v>25</v>
@@ -8893,7 +9025,7 @@
         <v>35</v>
       </c>
       <c r="G175" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H175" t="s">
         <v>216</v>
@@ -8904,10 +9036,10 @@
         <v>17</v>
       </c>
       <c r="C176" t="s">
-        <v>639</v>
+        <v>683</v>
       </c>
       <c r="D176" t="s">
-        <v>640</v>
+        <v>684</v>
       </c>
       <c r="E176" t="s">
         <v>25</v>
@@ -8916,7 +9048,7 @@
         <v>35</v>
       </c>
       <c r="G176" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H176" t="s">
         <v>216</v>
@@ -8927,10 +9059,10 @@
         <v>17</v>
       </c>
       <c r="C177" t="s">
-        <v>641</v>
+        <v>685</v>
       </c>
       <c r="D177" t="s">
-        <v>642</v>
+        <v>686</v>
       </c>
       <c r="E177" t="s">
         <v>25</v>
@@ -8939,7 +9071,7 @@
         <v>35</v>
       </c>
       <c r="G177" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H177" t="s">
         <v>216</v>
@@ -8950,10 +9082,10 @@
         <v>17</v>
       </c>
       <c r="C178" t="s">
-        <v>643</v>
+        <v>687</v>
       </c>
       <c r="D178" t="s">
-        <v>644</v>
+        <v>688</v>
       </c>
       <c r="E178" t="s">
         <v>25</v>
@@ -8962,7 +9094,7 @@
         <v>35</v>
       </c>
       <c r="G178" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H178" t="s">
         <v>216</v>
@@ -8973,10 +9105,10 @@
         <v>17</v>
       </c>
       <c r="C179" t="s">
-        <v>645</v>
+        <v>689</v>
       </c>
       <c r="D179" t="s">
-        <v>646</v>
+        <v>690</v>
       </c>
       <c r="E179" t="s">
         <v>25</v>
@@ -8985,7 +9117,7 @@
         <v>35</v>
       </c>
       <c r="G179" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H179" t="s">
         <v>216</v>
@@ -8996,10 +9128,10 @@
         <v>17</v>
       </c>
       <c r="C180" t="s">
-        <v>647</v>
+        <v>691</v>
       </c>
       <c r="D180" t="s">
-        <v>648</v>
+        <v>692</v>
       </c>
       <c r="E180" t="s">
         <v>25</v>
@@ -9008,7 +9140,7 @@
         <v>35</v>
       </c>
       <c r="G180" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H180" t="s">
         <v>216</v>
@@ -9019,10 +9151,10 @@
         <v>17</v>
       </c>
       <c r="C181" t="s">
-        <v>649</v>
+        <v>693</v>
       </c>
       <c r="D181" t="s">
-        <v>650</v>
+        <v>694</v>
       </c>
       <c r="E181" t="s">
         <v>25</v>
@@ -9031,7 +9163,7 @@
         <v>35</v>
       </c>
       <c r="G181" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H181" t="s">
         <v>216</v>
@@ -9042,10 +9174,10 @@
         <v>17</v>
       </c>
       <c r="C182" t="s">
-        <v>651</v>
+        <v>695</v>
       </c>
       <c r="D182" t="s">
-        <v>652</v>
+        <v>696</v>
       </c>
       <c r="E182" t="s">
         <v>25</v>
@@ -9054,7 +9186,7 @@
         <v>35</v>
       </c>
       <c r="G182" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H182" t="s">
         <v>216</v>
@@ -9065,10 +9197,10 @@
         <v>17</v>
       </c>
       <c r="C183" t="s">
-        <v>653</v>
+        <v>697</v>
       </c>
       <c r="D183" t="s">
-        <v>654</v>
+        <v>698</v>
       </c>
       <c r="E183" t="s">
         <v>25</v>
@@ -9077,7 +9209,7 @@
         <v>35</v>
       </c>
       <c r="G183" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H183" t="s">
         <v>216</v>
@@ -9088,10 +9220,10 @@
         <v>17</v>
       </c>
       <c r="C184" t="s">
-        <v>655</v>
+        <v>699</v>
       </c>
       <c r="D184" t="s">
-        <v>656</v>
+        <v>700</v>
       </c>
       <c r="E184" t="s">
         <v>25</v>
@@ -9100,7 +9232,7 @@
         <v>35</v>
       </c>
       <c r="G184" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H184" t="s">
         <v>216</v>
@@ -9111,10 +9243,10 @@
         <v>17</v>
       </c>
       <c r="C185" t="s">
-        <v>657</v>
+        <v>701</v>
       </c>
       <c r="D185" t="s">
-        <v>658</v>
+        <v>702</v>
       </c>
       <c r="E185" t="s">
         <v>25</v>
@@ -9123,7 +9255,7 @@
         <v>35</v>
       </c>
       <c r="G185" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H185" t="s">
         <v>216</v>
@@ -9134,10 +9266,10 @@
         <v>17</v>
       </c>
       <c r="C186" t="s">
-        <v>659</v>
+        <v>703</v>
       </c>
       <c r="D186" t="s">
-        <v>660</v>
+        <v>704</v>
       </c>
       <c r="E186" t="s">
         <v>25</v>
@@ -9146,7 +9278,7 @@
         <v>35</v>
       </c>
       <c r="G186" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H186" t="s">
         <v>216</v>
@@ -9157,10 +9289,10 @@
         <v>17</v>
       </c>
       <c r="C187" t="s">
-        <v>661</v>
+        <v>705</v>
       </c>
       <c r="D187" t="s">
-        <v>662</v>
+        <v>706</v>
       </c>
       <c r="E187" t="s">
         <v>25</v>
@@ -9169,7 +9301,7 @@
         <v>35</v>
       </c>
       <c r="G187" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H187" t="s">
         <v>216</v>
@@ -9180,10 +9312,10 @@
         <v>17</v>
       </c>
       <c r="C188" t="s">
-        <v>663</v>
+        <v>707</v>
       </c>
       <c r="D188" t="s">
-        <v>664</v>
+        <v>708</v>
       </c>
       <c r="E188" t="s">
         <v>25</v>
@@ -9192,7 +9324,7 @@
         <v>35</v>
       </c>
       <c r="G188" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H188" t="s">
         <v>216</v>
@@ -9203,10 +9335,10 @@
         <v>17</v>
       </c>
       <c r="C189" t="s">
-        <v>665</v>
+        <v>709</v>
       </c>
       <c r="D189" t="s">
-        <v>666</v>
+        <v>710</v>
       </c>
       <c r="E189" t="s">
         <v>25</v>
@@ -9215,7 +9347,7 @@
         <v>35</v>
       </c>
       <c r="G189" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H189" t="s">
         <v>216</v>
@@ -9226,10 +9358,10 @@
         <v>17</v>
       </c>
       <c r="C190" t="s">
-        <v>667</v>
+        <v>711</v>
       </c>
       <c r="D190" t="s">
-        <v>668</v>
+        <v>712</v>
       </c>
       <c r="E190" t="s">
         <v>25</v>
@@ -9238,7 +9370,7 @@
         <v>35</v>
       </c>
       <c r="G190" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H190" t="s">
         <v>216</v>
@@ -9249,10 +9381,10 @@
         <v>17</v>
       </c>
       <c r="C191" t="s">
-        <v>669</v>
+        <v>713</v>
       </c>
       <c r="D191" t="s">
-        <v>670</v>
+        <v>714</v>
       </c>
       <c r="E191" t="s">
         <v>25</v>
@@ -9261,7 +9393,7 @@
         <v>35</v>
       </c>
       <c r="G191" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H191" t="s">
         <v>216</v>
@@ -9272,10 +9404,10 @@
         <v>17</v>
       </c>
       <c r="C192" t="s">
-        <v>671</v>
+        <v>715</v>
       </c>
       <c r="D192" t="s">
-        <v>672</v>
+        <v>716</v>
       </c>
       <c r="E192" t="s">
         <v>25</v>
@@ -9284,7 +9416,7 @@
         <v>35</v>
       </c>
       <c r="G192" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H192" t="s">
         <v>216</v>
@@ -9295,10 +9427,10 @@
         <v>17</v>
       </c>
       <c r="C193" t="s">
-        <v>673</v>
+        <v>717</v>
       </c>
       <c r="D193" t="s">
-        <v>674</v>
+        <v>718</v>
       </c>
       <c r="E193" t="s">
         <v>25</v>
@@ -9307,7 +9439,7 @@
         <v>35</v>
       </c>
       <c r="G193" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H193" t="s">
         <v>216</v>
@@ -9318,10 +9450,10 @@
         <v>17</v>
       </c>
       <c r="C194" t="s">
-        <v>675</v>
+        <v>719</v>
       </c>
       <c r="D194" t="s">
-        <v>676</v>
+        <v>720</v>
       </c>
       <c r="E194" t="s">
         <v>25</v>
@@ -9330,7 +9462,7 @@
         <v>35</v>
       </c>
       <c r="G194" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H194" t="s">
         <v>216</v>
@@ -9341,10 +9473,10 @@
         <v>17</v>
       </c>
       <c r="C195" t="s">
-        <v>677</v>
+        <v>721</v>
       </c>
       <c r="D195" t="s">
-        <v>678</v>
+        <v>722</v>
       </c>
       <c r="E195" t="s">
         <v>25</v>
@@ -9353,7 +9485,7 @@
         <v>35</v>
       </c>
       <c r="G195" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H195" t="s">
         <v>216</v>
@@ -9364,10 +9496,10 @@
         <v>17</v>
       </c>
       <c r="C196" t="s">
-        <v>679</v>
+        <v>723</v>
       </c>
       <c r="D196" t="s">
-        <v>680</v>
+        <v>724</v>
       </c>
       <c r="E196" t="s">
         <v>25</v>
@@ -9376,7 +9508,7 @@
         <v>35</v>
       </c>
       <c r="G196" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H196" t="s">
         <v>216</v>
@@ -9387,10 +9519,10 @@
         <v>17</v>
       </c>
       <c r="C197" t="s">
-        <v>681</v>
+        <v>725</v>
       </c>
       <c r="D197" t="s">
-        <v>682</v>
+        <v>726</v>
       </c>
       <c r="E197" t="s">
         <v>25</v>
@@ -9399,7 +9531,7 @@
         <v>35</v>
       </c>
       <c r="G197" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H197" t="s">
         <v>216</v>
@@ -9410,10 +9542,10 @@
         <v>17</v>
       </c>
       <c r="C198" t="s">
-        <v>683</v>
+        <v>727</v>
       </c>
       <c r="D198" t="s">
-        <v>684</v>
+        <v>728</v>
       </c>
       <c r="E198" t="s">
         <v>25</v>
@@ -9422,7 +9554,7 @@
         <v>35</v>
       </c>
       <c r="G198" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H198" t="s">
         <v>216</v>
@@ -9433,10 +9565,10 @@
         <v>17</v>
       </c>
       <c r="C199" t="s">
-        <v>685</v>
+        <v>729</v>
       </c>
       <c r="D199" t="s">
-        <v>686</v>
+        <v>730</v>
       </c>
       <c r="E199" t="s">
         <v>25</v>
@@ -9445,7 +9577,7 @@
         <v>35</v>
       </c>
       <c r="G199" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H199" t="s">
         <v>216</v>
@@ -9456,10 +9588,10 @@
         <v>17</v>
       </c>
       <c r="C200" t="s">
-        <v>687</v>
+        <v>731</v>
       </c>
       <c r="D200" t="s">
-        <v>688</v>
+        <v>732</v>
       </c>
       <c r="E200" t="s">
         <v>25</v>
@@ -9468,7 +9600,7 @@
         <v>35</v>
       </c>
       <c r="G200" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H200" t="s">
         <v>216</v>
@@ -9479,10 +9611,10 @@
         <v>17</v>
       </c>
       <c r="C201" t="s">
-        <v>689</v>
+        <v>733</v>
       </c>
       <c r="D201" t="s">
-        <v>690</v>
+        <v>734</v>
       </c>
       <c r="E201" t="s">
         <v>25</v>
@@ -9491,7 +9623,7 @@
         <v>35</v>
       </c>
       <c r="G201" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H201" t="s">
         <v>216</v>
@@ -9502,10 +9634,10 @@
         <v>17</v>
       </c>
       <c r="C202" t="s">
-        <v>691</v>
+        <v>735</v>
       </c>
       <c r="D202" t="s">
-        <v>692</v>
+        <v>736</v>
       </c>
       <c r="E202" t="s">
         <v>25</v>
@@ -9514,7 +9646,7 @@
         <v>35</v>
       </c>
       <c r="G202" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H202" t="s">
         <v>216</v>
@@ -9525,10 +9657,10 @@
         <v>17</v>
       </c>
       <c r="C203" t="s">
-        <v>693</v>
+        <v>737</v>
       </c>
       <c r="D203" t="s">
-        <v>694</v>
+        <v>738</v>
       </c>
       <c r="E203" t="s">
         <v>25</v>
@@ -9537,7 +9669,7 @@
         <v>35</v>
       </c>
       <c r="G203" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H203" t="s">
         <v>216</v>
@@ -9548,10 +9680,10 @@
         <v>17</v>
       </c>
       <c r="C204" t="s">
-        <v>695</v>
+        <v>739</v>
       </c>
       <c r="D204" t="s">
-        <v>696</v>
+        <v>740</v>
       </c>
       <c r="E204" t="s">
         <v>25</v>
@@ -9560,7 +9692,7 @@
         <v>35</v>
       </c>
       <c r="G204" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H204" t="s">
         <v>216</v>
@@ -9571,10 +9703,10 @@
         <v>17</v>
       </c>
       <c r="C205" t="s">
-        <v>697</v>
+        <v>741</v>
       </c>
       <c r="D205" t="s">
-        <v>698</v>
+        <v>742</v>
       </c>
       <c r="E205" t="s">
         <v>25</v>
@@ -9583,7 +9715,7 @@
         <v>35</v>
       </c>
       <c r="G205" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H205" t="s">
         <v>216</v>
@@ -9594,10 +9726,10 @@
         <v>17</v>
       </c>
       <c r="C206" t="s">
-        <v>699</v>
+        <v>743</v>
       </c>
       <c r="D206" t="s">
-        <v>700</v>
+        <v>744</v>
       </c>
       <c r="E206" t="s">
         <v>25</v>
@@ -9606,7 +9738,7 @@
         <v>35</v>
       </c>
       <c r="G206" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H206" t="s">
         <v>216</v>
@@ -9617,10 +9749,10 @@
         <v>17</v>
       </c>
       <c r="C207" t="s">
-        <v>701</v>
+        <v>745</v>
       </c>
       <c r="D207" t="s">
-        <v>702</v>
+        <v>746</v>
       </c>
       <c r="E207" t="s">
         <v>25</v>
@@ -9629,7 +9761,7 @@
         <v>35</v>
       </c>
       <c r="G207" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H207" t="s">
         <v>216</v>
@@ -9640,10 +9772,10 @@
         <v>17</v>
       </c>
       <c r="C208" t="s">
-        <v>703</v>
+        <v>747</v>
       </c>
       <c r="D208" t="s">
-        <v>704</v>
+        <v>748</v>
       </c>
       <c r="E208" t="s">
         <v>25</v>
@@ -9652,7 +9784,7 @@
         <v>35</v>
       </c>
       <c r="G208" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H208" t="s">
         <v>216</v>
@@ -9663,10 +9795,10 @@
         <v>17</v>
       </c>
       <c r="C209" t="s">
-        <v>705</v>
+        <v>749</v>
       </c>
       <c r="D209" t="s">
-        <v>706</v>
+        <v>750</v>
       </c>
       <c r="E209" t="s">
         <v>25</v>
@@ -9675,7 +9807,7 @@
         <v>35</v>
       </c>
       <c r="G209" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H209" t="s">
         <v>216</v>
@@ -9686,10 +9818,10 @@
         <v>17</v>
       </c>
       <c r="C210" t="s">
-        <v>707</v>
+        <v>751</v>
       </c>
       <c r="D210" t="s">
-        <v>708</v>
+        <v>752</v>
       </c>
       <c r="E210" t="s">
         <v>25</v>
@@ -9698,7 +9830,7 @@
         <v>35</v>
       </c>
       <c r="G210" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H210" t="s">
         <v>216</v>
@@ -9709,10 +9841,10 @@
         <v>17</v>
       </c>
       <c r="C211" t="s">
-        <v>709</v>
+        <v>753</v>
       </c>
       <c r="D211" t="s">
-        <v>710</v>
+        <v>754</v>
       </c>
       <c r="E211" t="s">
         <v>25</v>
@@ -9721,7 +9853,7 @@
         <v>35</v>
       </c>
       <c r="G211" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H211" t="s">
         <v>216</v>
@@ -9732,10 +9864,10 @@
         <v>17</v>
       </c>
       <c r="C212" t="s">
-        <v>711</v>
+        <v>755</v>
       </c>
       <c r="D212" t="s">
-        <v>712</v>
+        <v>756</v>
       </c>
       <c r="E212" t="s">
         <v>25</v>
@@ -9744,7 +9876,7 @@
         <v>35</v>
       </c>
       <c r="G212" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H212" t="s">
         <v>216</v>
@@ -9755,10 +9887,10 @@
         <v>17</v>
       </c>
       <c r="C213" t="s">
-        <v>713</v>
+        <v>757</v>
       </c>
       <c r="D213" t="s">
-        <v>714</v>
+        <v>758</v>
       </c>
       <c r="E213" t="s">
         <v>25</v>
@@ -9767,7 +9899,7 @@
         <v>35</v>
       </c>
       <c r="G213" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H213" t="s">
         <v>216</v>
@@ -9778,10 +9910,10 @@
         <v>17</v>
       </c>
       <c r="C214" t="s">
-        <v>715</v>
+        <v>759</v>
       </c>
       <c r="D214" t="s">
-        <v>716</v>
+        <v>760</v>
       </c>
       <c r="E214" t="s">
         <v>25</v>
@@ -9790,7 +9922,7 @@
         <v>35</v>
       </c>
       <c r="G214" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H214" t="s">
         <v>216</v>
@@ -9801,10 +9933,10 @@
         <v>17</v>
       </c>
       <c r="C215" t="s">
-        <v>717</v>
+        <v>761</v>
       </c>
       <c r="D215" t="s">
-        <v>718</v>
+        <v>762</v>
       </c>
       <c r="E215" t="s">
         <v>25</v>
@@ -9813,7 +9945,7 @@
         <v>35</v>
       </c>
       <c r="G215" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H215" t="s">
         <v>216</v>
@@ -9824,10 +9956,10 @@
         <v>17</v>
       </c>
       <c r="C216" t="s">
-        <v>719</v>
+        <v>763</v>
       </c>
       <c r="D216" t="s">
-        <v>720</v>
+        <v>764</v>
       </c>
       <c r="E216" t="s">
         <v>25</v>
@@ -9836,7 +9968,7 @@
         <v>35</v>
       </c>
       <c r="G216" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H216" t="s">
         <v>216</v>
@@ -9847,10 +9979,10 @@
         <v>17</v>
       </c>
       <c r="C217" t="s">
-        <v>721</v>
+        <v>765</v>
       </c>
       <c r="D217" t="s">
-        <v>722</v>
+        <v>766</v>
       </c>
       <c r="E217" t="s">
         <v>25</v>
@@ -9859,7 +9991,7 @@
         <v>35</v>
       </c>
       <c r="G217" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H217" t="s">
         <v>216</v>
@@ -9870,10 +10002,10 @@
         <v>17</v>
       </c>
       <c r="C218" t="s">
-        <v>723</v>
+        <v>767</v>
       </c>
       <c r="D218" t="s">
-        <v>724</v>
+        <v>768</v>
       </c>
       <c r="E218" t="s">
         <v>25</v>
@@ -9882,7 +10014,7 @@
         <v>35</v>
       </c>
       <c r="G218" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H218" t="s">
         <v>216</v>
@@ -9893,10 +10025,10 @@
         <v>17</v>
       </c>
       <c r="C219" t="s">
-        <v>725</v>
+        <v>769</v>
       </c>
       <c r="D219" t="s">
-        <v>726</v>
+        <v>770</v>
       </c>
       <c r="E219" t="s">
         <v>25</v>
@@ -9905,7 +10037,7 @@
         <v>35</v>
       </c>
       <c r="G219" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H219" t="s">
         <v>216</v>
@@ -9916,10 +10048,10 @@
         <v>17</v>
       </c>
       <c r="C220" t="s">
-        <v>727</v>
+        <v>771</v>
       </c>
       <c r="D220" t="s">
-        <v>728</v>
+        <v>772</v>
       </c>
       <c r="E220" t="s">
         <v>25</v>
@@ -9928,7 +10060,7 @@
         <v>35</v>
       </c>
       <c r="G220" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H220" t="s">
         <v>216</v>
@@ -9939,10 +10071,10 @@
         <v>17</v>
       </c>
       <c r="C221" t="s">
-        <v>729</v>
+        <v>773</v>
       </c>
       <c r="D221" t="s">
-        <v>730</v>
+        <v>774</v>
       </c>
       <c r="E221" t="s">
         <v>25</v>
@@ -9951,7 +10083,7 @@
         <v>35</v>
       </c>
       <c r="G221" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H221" t="s">
         <v>216</v>
@@ -9962,10 +10094,10 @@
         <v>17</v>
       </c>
       <c r="C222" t="s">
-        <v>731</v>
+        <v>775</v>
       </c>
       <c r="D222" t="s">
-        <v>732</v>
+        <v>776</v>
       </c>
       <c r="E222" t="s">
         <v>25</v>
@@ -9974,7 +10106,7 @@
         <v>35</v>
       </c>
       <c r="G222" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H222" t="s">
         <v>216</v>
@@ -9985,10 +10117,10 @@
         <v>17</v>
       </c>
       <c r="C223" t="s">
-        <v>733</v>
+        <v>777</v>
       </c>
       <c r="D223" t="s">
-        <v>734</v>
+        <v>778</v>
       </c>
       <c r="E223" t="s">
         <v>25</v>
@@ -9997,7 +10129,7 @@
         <v>35</v>
       </c>
       <c r="G223" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H223" t="s">
         <v>216</v>
@@ -10008,10 +10140,10 @@
         <v>17</v>
       </c>
       <c r="C224" t="s">
-        <v>735</v>
+        <v>779</v>
       </c>
       <c r="D224" t="s">
-        <v>736</v>
+        <v>780</v>
       </c>
       <c r="E224" t="s">
         <v>25</v>
@@ -10020,7 +10152,7 @@
         <v>35</v>
       </c>
       <c r="G224" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H224" t="s">
         <v>216</v>
@@ -10031,10 +10163,10 @@
         <v>17</v>
       </c>
       <c r="C225" t="s">
-        <v>737</v>
+        <v>781</v>
       </c>
       <c r="D225" t="s">
-        <v>738</v>
+        <v>782</v>
       </c>
       <c r="E225" t="s">
         <v>25</v>
@@ -10043,7 +10175,7 @@
         <v>35</v>
       </c>
       <c r="G225" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H225" t="s">
         <v>216</v>
@@ -10054,10 +10186,10 @@
         <v>17</v>
       </c>
       <c r="C226" t="s">
-        <v>739</v>
+        <v>783</v>
       </c>
       <c r="D226" t="s">
-        <v>740</v>
+        <v>784</v>
       </c>
       <c r="E226" t="s">
         <v>25</v>
@@ -10066,7 +10198,7 @@
         <v>35</v>
       </c>
       <c r="G226" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H226" t="s">
         <v>216</v>
@@ -10077,10 +10209,10 @@
         <v>17</v>
       </c>
       <c r="C227" t="s">
-        <v>741</v>
+        <v>785</v>
       </c>
       <c r="D227" t="s">
-        <v>742</v>
+        <v>786</v>
       </c>
       <c r="E227" t="s">
         <v>25</v>
@@ -10089,7 +10221,7 @@
         <v>35</v>
       </c>
       <c r="G227" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H227" t="s">
         <v>216</v>
@@ -10100,10 +10232,10 @@
         <v>17</v>
       </c>
       <c r="C228" t="s">
-        <v>743</v>
+        <v>787</v>
       </c>
       <c r="D228" t="s">
-        <v>744</v>
+        <v>788</v>
       </c>
       <c r="E228" t="s">
         <v>25</v>
@@ -10112,7 +10244,7 @@
         <v>35</v>
       </c>
       <c r="G228" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H228" t="s">
         <v>216</v>
@@ -10123,10 +10255,10 @@
         <v>17</v>
       </c>
       <c r="C229" t="s">
-        <v>745</v>
+        <v>789</v>
       </c>
       <c r="D229" t="s">
-        <v>746</v>
+        <v>790</v>
       </c>
       <c r="E229" t="s">
         <v>25</v>
@@ -10135,7 +10267,7 @@
         <v>35</v>
       </c>
       <c r="G229" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H229" t="s">
         <v>216</v>
@@ -10146,10 +10278,10 @@
         <v>17</v>
       </c>
       <c r="C230" t="s">
-        <v>747</v>
+        <v>791</v>
       </c>
       <c r="D230" t="s">
-        <v>748</v>
+        <v>792</v>
       </c>
       <c r="E230" t="s">
         <v>25</v>
@@ -10158,7 +10290,7 @@
         <v>35</v>
       </c>
       <c r="G230" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H230" t="s">
         <v>216</v>
@@ -10169,10 +10301,10 @@
         <v>17</v>
       </c>
       <c r="C231" t="s">
-        <v>749</v>
+        <v>793</v>
       </c>
       <c r="D231" t="s">
-        <v>750</v>
+        <v>794</v>
       </c>
       <c r="E231" t="s">
         <v>25</v>
@@ -10181,7 +10313,7 @@
         <v>35</v>
       </c>
       <c r="G231" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H231" t="s">
         <v>216</v>
@@ -10192,10 +10324,10 @@
         <v>17</v>
       </c>
       <c r="C232" t="s">
-        <v>751</v>
+        <v>795</v>
       </c>
       <c r="D232" t="s">
-        <v>752</v>
+        <v>796</v>
       </c>
       <c r="E232" t="s">
         <v>25</v>
@@ -10204,7 +10336,7 @@
         <v>35</v>
       </c>
       <c r="G232" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H232" t="s">
         <v>216</v>
@@ -10215,10 +10347,10 @@
         <v>17</v>
       </c>
       <c r="C233" t="s">
-        <v>753</v>
+        <v>797</v>
       </c>
       <c r="D233" t="s">
-        <v>754</v>
+        <v>798</v>
       </c>
       <c r="E233" t="s">
         <v>25</v>
@@ -10227,7 +10359,7 @@
         <v>35</v>
       </c>
       <c r="G233" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H233" t="s">
         <v>216</v>
@@ -10238,10 +10370,10 @@
         <v>17</v>
       </c>
       <c r="C234" t="s">
-        <v>755</v>
+        <v>799</v>
       </c>
       <c r="D234" t="s">
-        <v>756</v>
+        <v>800</v>
       </c>
       <c r="E234" t="s">
         <v>25</v>
@@ -10250,7 +10382,7 @@
         <v>35</v>
       </c>
       <c r="G234" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H234" t="s">
         <v>216</v>
@@ -10261,10 +10393,10 @@
         <v>17</v>
       </c>
       <c r="C235" t="s">
-        <v>757</v>
+        <v>801</v>
       </c>
       <c r="D235" t="s">
-        <v>758</v>
+        <v>802</v>
       </c>
       <c r="E235" t="s">
         <v>25</v>
@@ -10273,7 +10405,7 @@
         <v>35</v>
       </c>
       <c r="G235" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H235" t="s">
         <v>216</v>
@@ -10284,10 +10416,10 @@
         <v>17</v>
       </c>
       <c r="C236" t="s">
-        <v>759</v>
+        <v>803</v>
       </c>
       <c r="D236" t="s">
-        <v>760</v>
+        <v>804</v>
       </c>
       <c r="E236" t="s">
         <v>25</v>
@@ -10296,7 +10428,7 @@
         <v>35</v>
       </c>
       <c r="G236" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H236" t="s">
         <v>216</v>
@@ -10307,10 +10439,10 @@
         <v>17</v>
       </c>
       <c r="C237" t="s">
-        <v>761</v>
+        <v>805</v>
       </c>
       <c r="D237" t="s">
-        <v>762</v>
+        <v>806</v>
       </c>
       <c r="E237" t="s">
         <v>25</v>
@@ -10319,7 +10451,7 @@
         <v>35</v>
       </c>
       <c r="G237" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H237" t="s">
         <v>216</v>
@@ -10330,10 +10462,10 @@
         <v>17</v>
       </c>
       <c r="C238" t="s">
-        <v>763</v>
+        <v>807</v>
       </c>
       <c r="D238" t="s">
-        <v>764</v>
+        <v>808</v>
       </c>
       <c r="E238" t="s">
         <v>25</v>
@@ -10342,7 +10474,7 @@
         <v>35</v>
       </c>
       <c r="G238" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H238" t="s">
         <v>216</v>
@@ -10353,10 +10485,10 @@
         <v>17</v>
       </c>
       <c r="C239" t="s">
-        <v>765</v>
+        <v>809</v>
       </c>
       <c r="D239" t="s">
-        <v>766</v>
+        <v>810</v>
       </c>
       <c r="E239" t="s">
         <v>25</v>
@@ -10365,7 +10497,7 @@
         <v>35</v>
       </c>
       <c r="G239" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H239" t="s">
         <v>216</v>
@@ -10376,10 +10508,10 @@
         <v>17</v>
       </c>
       <c r="C240" t="s">
-        <v>767</v>
+        <v>811</v>
       </c>
       <c r="D240" t="s">
-        <v>768</v>
+        <v>812</v>
       </c>
       <c r="E240" t="s">
         <v>25</v>
@@ -10388,7 +10520,7 @@
         <v>35</v>
       </c>
       <c r="G240" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H240" t="s">
         <v>216</v>
@@ -10399,10 +10531,10 @@
         <v>17</v>
       </c>
       <c r="C241" t="s">
-        <v>769</v>
+        <v>813</v>
       </c>
       <c r="D241" t="s">
-        <v>770</v>
+        <v>814</v>
       </c>
       <c r="E241" t="s">
         <v>25</v>
@@ -10411,7 +10543,7 @@
         <v>35</v>
       </c>
       <c r="G241" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H241" t="s">
         <v>216</v>
@@ -10422,10 +10554,10 @@
         <v>17</v>
       </c>
       <c r="C242" t="s">
-        <v>771</v>
+        <v>815</v>
       </c>
       <c r="D242" t="s">
-        <v>772</v>
+        <v>816</v>
       </c>
       <c r="E242" t="s">
         <v>25</v>
@@ -10434,7 +10566,7 @@
         <v>35</v>
       </c>
       <c r="G242" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H242" t="s">
         <v>216</v>
@@ -10445,10 +10577,10 @@
         <v>17</v>
       </c>
       <c r="C243" t="s">
-        <v>773</v>
+        <v>817</v>
       </c>
       <c r="D243" t="s">
-        <v>774</v>
+        <v>818</v>
       </c>
       <c r="E243" t="s">
         <v>25</v>
@@ -10457,7 +10589,7 @@
         <v>35</v>
       </c>
       <c r="G243" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H243" t="s">
         <v>216</v>
@@ -10468,10 +10600,10 @@
         <v>17</v>
       </c>
       <c r="C244" t="s">
-        <v>775</v>
+        <v>819</v>
       </c>
       <c r="D244" t="s">
-        <v>776</v>
+        <v>820</v>
       </c>
       <c r="E244" t="s">
         <v>25</v>
@@ -10480,7 +10612,7 @@
         <v>35</v>
       </c>
       <c r="G244" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H244" t="s">
         <v>216</v>
@@ -10491,10 +10623,10 @@
         <v>17</v>
       </c>
       <c r="C245" t="s">
-        <v>777</v>
+        <v>821</v>
       </c>
       <c r="D245" t="s">
-        <v>778</v>
+        <v>822</v>
       </c>
       <c r="E245" t="s">
         <v>25</v>
@@ -10503,7 +10635,7 @@
         <v>35</v>
       </c>
       <c r="G245" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H245" t="s">
         <v>216</v>
@@ -10514,10 +10646,10 @@
         <v>17</v>
       </c>
       <c r="C246" t="s">
-        <v>779</v>
+        <v>823</v>
       </c>
       <c r="D246" t="s">
-        <v>780</v>
+        <v>824</v>
       </c>
       <c r="E246" t="s">
         <v>25</v>
@@ -10526,7 +10658,7 @@
         <v>35</v>
       </c>
       <c r="G246" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H246" t="s">
         <v>216</v>
@@ -10537,10 +10669,10 @@
         <v>17</v>
       </c>
       <c r="C247" t="s">
-        <v>781</v>
+        <v>825</v>
       </c>
       <c r="D247" t="s">
-        <v>782</v>
+        <v>826</v>
       </c>
       <c r="E247" t="s">
         <v>25</v>
@@ -10549,7 +10681,7 @@
         <v>35</v>
       </c>
       <c r="G247" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H247" t="s">
         <v>216</v>
@@ -10560,10 +10692,10 @@
         <v>17</v>
       </c>
       <c r="C248" t="s">
-        <v>783</v>
+        <v>827</v>
       </c>
       <c r="D248" t="s">
-        <v>784</v>
+        <v>828</v>
       </c>
       <c r="E248" t="s">
         <v>25</v>
@@ -10572,7 +10704,7 @@
         <v>35</v>
       </c>
       <c r="G248" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H248" t="s">
         <v>216</v>
@@ -10583,10 +10715,10 @@
         <v>17</v>
       </c>
       <c r="C249" t="s">
-        <v>785</v>
+        <v>829</v>
       </c>
       <c r="D249" t="s">
-        <v>786</v>
+        <v>830</v>
       </c>
       <c r="E249" t="s">
         <v>25</v>
@@ -10595,7 +10727,7 @@
         <v>35</v>
       </c>
       <c r="G249" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H249" t="s">
         <v>216</v>
@@ -10606,10 +10738,10 @@
         <v>17</v>
       </c>
       <c r="C250" t="s">
-        <v>787</v>
+        <v>831</v>
       </c>
       <c r="D250" t="s">
-        <v>788</v>
+        <v>832</v>
       </c>
       <c r="E250" t="s">
         <v>25</v>
@@ -10618,7 +10750,7 @@
         <v>35</v>
       </c>
       <c r="G250" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H250" t="s">
         <v>216</v>
@@ -10629,10 +10761,10 @@
         <v>17</v>
       </c>
       <c r="C251" t="s">
-        <v>789</v>
+        <v>833</v>
       </c>
       <c r="D251" t="s">
-        <v>790</v>
+        <v>834</v>
       </c>
       <c r="E251" t="s">
         <v>25</v>
@@ -10641,7 +10773,7 @@
         <v>35</v>
       </c>
       <c r="G251" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H251" t="s">
         <v>216</v>
@@ -10652,10 +10784,10 @@
         <v>17</v>
       </c>
       <c r="C252" t="s">
-        <v>791</v>
+        <v>835</v>
       </c>
       <c r="D252" t="s">
-        <v>792</v>
+        <v>836</v>
       </c>
       <c r="E252" t="s">
         <v>25</v>
@@ -10664,7 +10796,7 @@
         <v>35</v>
       </c>
       <c r="G252" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H252" t="s">
         <v>216</v>
@@ -10675,10 +10807,10 @@
         <v>17</v>
       </c>
       <c r="C253" t="s">
-        <v>793</v>
+        <v>837</v>
       </c>
       <c r="D253" t="s">
-        <v>794</v>
+        <v>838</v>
       </c>
       <c r="E253" t="s">
         <v>25</v>
@@ -10687,7 +10819,7 @@
         <v>35</v>
       </c>
       <c r="G253" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H253" t="s">
         <v>216</v>
@@ -10698,10 +10830,10 @@
         <v>17</v>
       </c>
       <c r="C254" t="s">
-        <v>795</v>
+        <v>839</v>
       </c>
       <c r="D254" t="s">
-        <v>796</v>
+        <v>840</v>
       </c>
       <c r="E254" t="s">
         <v>25</v>
@@ -10710,7 +10842,7 @@
         <v>35</v>
       </c>
       <c r="G254" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H254" t="s">
         <v>216</v>
@@ -10721,10 +10853,10 @@
         <v>17</v>
       </c>
       <c r="C255" t="s">
-        <v>797</v>
+        <v>841</v>
       </c>
       <c r="D255" t="s">
-        <v>798</v>
+        <v>842</v>
       </c>
       <c r="E255" t="s">
         <v>25</v>
@@ -10733,7 +10865,7 @@
         <v>35</v>
       </c>
       <c r="G255" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H255" t="s">
         <v>216</v>
@@ -10744,10 +10876,10 @@
         <v>17</v>
       </c>
       <c r="C256" t="s">
-        <v>799</v>
+        <v>843</v>
       </c>
       <c r="D256" t="s">
-        <v>800</v>
+        <v>844</v>
       </c>
       <c r="E256" t="s">
         <v>25</v>
@@ -10756,7 +10888,7 @@
         <v>35</v>
       </c>
       <c r="G256" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H256" t="s">
         <v>216</v>
@@ -10767,10 +10899,10 @@
         <v>17</v>
       </c>
       <c r="C257" t="s">
-        <v>801</v>
+        <v>845</v>
       </c>
       <c r="D257" t="s">
-        <v>802</v>
+        <v>846</v>
       </c>
       <c r="E257" t="s">
         <v>25</v>
@@ -10779,7 +10911,7 @@
         <v>35</v>
       </c>
       <c r="G257" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H257" t="s">
         <v>216</v>
@@ -10790,10 +10922,10 @@
         <v>17</v>
       </c>
       <c r="C258" t="s">
-        <v>803</v>
+        <v>847</v>
       </c>
       <c r="D258" t="s">
-        <v>804</v>
+        <v>848</v>
       </c>
       <c r="E258" t="s">
         <v>25</v>
@@ -10802,7 +10934,7 @@
         <v>35</v>
       </c>
       <c r="G258" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H258" t="s">
         <v>216</v>
@@ -10813,10 +10945,10 @@
         <v>17</v>
       </c>
       <c r="C259" t="s">
-        <v>805</v>
+        <v>849</v>
       </c>
       <c r="D259" t="s">
-        <v>806</v>
+        <v>850</v>
       </c>
       <c r="E259" t="s">
         <v>25</v>
@@ -10825,7 +10957,7 @@
         <v>35</v>
       </c>
       <c r="G259" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H259" t="s">
         <v>216</v>
@@ -10836,10 +10968,10 @@
         <v>17</v>
       </c>
       <c r="C260" t="s">
-        <v>807</v>
+        <v>851</v>
       </c>
       <c r="D260" t="s">
-        <v>808</v>
+        <v>852</v>
       </c>
       <c r="E260" t="s">
         <v>25</v>
@@ -10848,7 +10980,7 @@
         <v>35</v>
       </c>
       <c r="G260" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H260" t="s">
         <v>216</v>
@@ -10859,10 +10991,10 @@
         <v>17</v>
       </c>
       <c r="C261" t="s">
-        <v>809</v>
+        <v>853</v>
       </c>
       <c r="D261" t="s">
-        <v>810</v>
+        <v>854</v>
       </c>
       <c r="E261" t="s">
         <v>25</v>
@@ -10871,7 +11003,7 @@
         <v>35</v>
       </c>
       <c r="G261" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H261" t="s">
         <v>216</v>
@@ -10882,10 +11014,10 @@
         <v>17</v>
       </c>
       <c r="C262" t="s">
-        <v>811</v>
+        <v>855</v>
       </c>
       <c r="D262" t="s">
-        <v>812</v>
+        <v>856</v>
       </c>
       <c r="E262" t="s">
         <v>25</v>
@@ -10894,7 +11026,7 @@
         <v>35</v>
       </c>
       <c r="G262" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H262" t="s">
         <v>216</v>
@@ -10905,10 +11037,10 @@
         <v>17</v>
       </c>
       <c r="C263" t="s">
-        <v>813</v>
+        <v>857</v>
       </c>
       <c r="D263" t="s">
-        <v>814</v>
+        <v>858</v>
       </c>
       <c r="E263" t="s">
         <v>25</v>
@@ -10917,7 +11049,7 @@
         <v>35</v>
       </c>
       <c r="G263" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H263" t="s">
         <v>216</v>
@@ -10928,10 +11060,10 @@
         <v>17</v>
       </c>
       <c r="C264" t="s">
-        <v>815</v>
+        <v>859</v>
       </c>
       <c r="D264" t="s">
-        <v>816</v>
+        <v>860</v>
       </c>
       <c r="E264" t="s">
         <v>25</v>
@@ -10940,7 +11072,7 @@
         <v>35</v>
       </c>
       <c r="G264" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H264" t="s">
         <v>216</v>
@@ -10951,10 +11083,10 @@
         <v>17</v>
       </c>
       <c r="C265" t="s">
-        <v>817</v>
+        <v>861</v>
       </c>
       <c r="D265" t="s">
-        <v>818</v>
+        <v>862</v>
       </c>
       <c r="E265" t="s">
         <v>25</v>
@@ -10963,7 +11095,7 @@
         <v>35</v>
       </c>
       <c r="G265" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H265" t="s">
         <v>216</v>
@@ -10974,10 +11106,10 @@
         <v>17</v>
       </c>
       <c r="C266" t="s">
-        <v>819</v>
+        <v>863</v>
       </c>
       <c r="D266" t="s">
-        <v>820</v>
+        <v>864</v>
       </c>
       <c r="E266" t="s">
         <v>25</v>
@@ -10986,7 +11118,7 @@
         <v>35</v>
       </c>
       <c r="G266" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H266" t="s">
         <v>216</v>
@@ -10997,10 +11129,10 @@
         <v>17</v>
       </c>
       <c r="C267" t="s">
-        <v>821</v>
+        <v>865</v>
       </c>
       <c r="D267" t="s">
-        <v>822</v>
+        <v>866</v>
       </c>
       <c r="E267" t="s">
         <v>25</v>
@@ -11009,7 +11141,7 @@
         <v>35</v>
       </c>
       <c r="G267" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H267" t="s">
         <v>216</v>
@@ -11020,10 +11152,10 @@
         <v>17</v>
       </c>
       <c r="C268" t="s">
-        <v>823</v>
+        <v>867</v>
       </c>
       <c r="D268" t="s">
-        <v>824</v>
+        <v>868</v>
       </c>
       <c r="E268" t="s">
         <v>25</v>
@@ -11032,7 +11164,7 @@
         <v>35</v>
       </c>
       <c r="G268" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H268" t="s">
         <v>216</v>
@@ -11043,10 +11175,10 @@
         <v>17</v>
       </c>
       <c r="C269" t="s">
-        <v>825</v>
+        <v>869</v>
       </c>
       <c r="D269" t="s">
-        <v>826</v>
+        <v>870</v>
       </c>
       <c r="E269" t="s">
         <v>25</v>
@@ -11055,7 +11187,7 @@
         <v>35</v>
       </c>
       <c r="G269" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="H269" t="s">
         <v>216</v>
@@ -11068,7 +11200,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
-  <dimension ref="B3:R44"/>
+  <dimension ref="B3:R66"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="11.19921875" bestFit="1" customWidth="1"/>
@@ -12163,6 +12295,446 @@
         <v>35</v>
       </c>
       <c r="R44" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="45" spans="13:18">
+      <c r="M45" t="s">
+        <v>17</v>
+      </c>
+      <c r="N45" t="s">
+        <v>295</v>
+      </c>
+      <c r="O45" t="s">
+        <v>296</v>
+      </c>
+      <c r="P45" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>35</v>
+      </c>
+      <c r="R45" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="46" spans="13:18">
+      <c r="M46" t="s">
+        <v>17</v>
+      </c>
+      <c r="N46" t="s">
+        <v>297</v>
+      </c>
+      <c r="O46" t="s">
+        <v>298</v>
+      </c>
+      <c r="P46" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>35</v>
+      </c>
+      <c r="R46" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="47" spans="13:18">
+      <c r="M47" t="s">
+        <v>17</v>
+      </c>
+      <c r="N47" t="s">
+        <v>299</v>
+      </c>
+      <c r="O47" t="s">
+        <v>300</v>
+      </c>
+      <c r="P47" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>35</v>
+      </c>
+      <c r="R47" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="48" spans="13:18">
+      <c r="M48" t="s">
+        <v>17</v>
+      </c>
+      <c r="N48" t="s">
+        <v>301</v>
+      </c>
+      <c r="O48" t="s">
+        <v>302</v>
+      </c>
+      <c r="P48" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>35</v>
+      </c>
+      <c r="R48" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="49" spans="13:18">
+      <c r="M49" t="s">
+        <v>17</v>
+      </c>
+      <c r="N49" t="s">
+        <v>303</v>
+      </c>
+      <c r="O49" t="s">
+        <v>304</v>
+      </c>
+      <c r="P49" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>35</v>
+      </c>
+      <c r="R49" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="50" spans="13:18">
+      <c r="M50" t="s">
+        <v>17</v>
+      </c>
+      <c r="N50" t="s">
+        <v>305</v>
+      </c>
+      <c r="O50" t="s">
+        <v>306</v>
+      </c>
+      <c r="P50" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>35</v>
+      </c>
+      <c r="R50" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="51" spans="13:18">
+      <c r="M51" t="s">
+        <v>17</v>
+      </c>
+      <c r="N51" t="s">
+        <v>307</v>
+      </c>
+      <c r="O51" t="s">
+        <v>308</v>
+      </c>
+      <c r="P51" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>35</v>
+      </c>
+      <c r="R51" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="52" spans="13:18">
+      <c r="M52" t="s">
+        <v>17</v>
+      </c>
+      <c r="N52" t="s">
+        <v>309</v>
+      </c>
+      <c r="O52" t="s">
+        <v>310</v>
+      </c>
+      <c r="P52" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>35</v>
+      </c>
+      <c r="R52" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="53" spans="13:18">
+      <c r="M53" t="s">
+        <v>17</v>
+      </c>
+      <c r="N53" t="s">
+        <v>311</v>
+      </c>
+      <c r="O53" t="s">
+        <v>312</v>
+      </c>
+      <c r="P53" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>35</v>
+      </c>
+      <c r="R53" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="54" spans="13:18">
+      <c r="M54" t="s">
+        <v>17</v>
+      </c>
+      <c r="N54" t="s">
+        <v>313</v>
+      </c>
+      <c r="O54" t="s">
+        <v>314</v>
+      </c>
+      <c r="P54" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>35</v>
+      </c>
+      <c r="R54" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="55" spans="13:18">
+      <c r="M55" t="s">
+        <v>17</v>
+      </c>
+      <c r="N55" t="s">
+        <v>315</v>
+      </c>
+      <c r="O55" t="s">
+        <v>316</v>
+      </c>
+      <c r="P55" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>35</v>
+      </c>
+      <c r="R55" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="56" spans="13:18">
+      <c r="M56" t="s">
+        <v>17</v>
+      </c>
+      <c r="N56" t="s">
+        <v>317</v>
+      </c>
+      <c r="O56" t="s">
+        <v>318</v>
+      </c>
+      <c r="P56" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>35</v>
+      </c>
+      <c r="R56" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="57" spans="13:18">
+      <c r="M57" t="s">
+        <v>17</v>
+      </c>
+      <c r="N57" t="s">
+        <v>319</v>
+      </c>
+      <c r="O57" t="s">
+        <v>320</v>
+      </c>
+      <c r="P57" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>35</v>
+      </c>
+      <c r="R57" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="58" spans="13:18">
+      <c r="M58" t="s">
+        <v>17</v>
+      </c>
+      <c r="N58" t="s">
+        <v>321</v>
+      </c>
+      <c r="O58" t="s">
+        <v>322</v>
+      </c>
+      <c r="P58" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>35</v>
+      </c>
+      <c r="R58" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="59" spans="13:18">
+      <c r="M59" t="s">
+        <v>17</v>
+      </c>
+      <c r="N59" t="s">
+        <v>323</v>
+      </c>
+      <c r="O59" t="s">
+        <v>324</v>
+      </c>
+      <c r="P59" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>35</v>
+      </c>
+      <c r="R59" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="60" spans="13:18">
+      <c r="M60" t="s">
+        <v>17</v>
+      </c>
+      <c r="N60" t="s">
+        <v>325</v>
+      </c>
+      <c r="O60" t="s">
+        <v>326</v>
+      </c>
+      <c r="P60" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>35</v>
+      </c>
+      <c r="R60" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="61" spans="13:18">
+      <c r="M61" t="s">
+        <v>17</v>
+      </c>
+      <c r="N61" t="s">
+        <v>327</v>
+      </c>
+      <c r="O61" t="s">
+        <v>328</v>
+      </c>
+      <c r="P61" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>35</v>
+      </c>
+      <c r="R61" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="62" spans="13:18">
+      <c r="M62" t="s">
+        <v>17</v>
+      </c>
+      <c r="N62" t="s">
+        <v>329</v>
+      </c>
+      <c r="O62" t="s">
+        <v>330</v>
+      </c>
+      <c r="P62" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>35</v>
+      </c>
+      <c r="R62" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="63" spans="13:18">
+      <c r="M63" t="s">
+        <v>17</v>
+      </c>
+      <c r="N63" t="s">
+        <v>331</v>
+      </c>
+      <c r="O63" t="s">
+        <v>332</v>
+      </c>
+      <c r="P63" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>35</v>
+      </c>
+      <c r="R63" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="64" spans="13:18">
+      <c r="M64" t="s">
+        <v>17</v>
+      </c>
+      <c r="N64" t="s">
+        <v>333</v>
+      </c>
+      <c r="O64" t="s">
+        <v>334</v>
+      </c>
+      <c r="P64" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>35</v>
+      </c>
+      <c r="R64" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="65" spans="13:18">
+      <c r="M65" t="s">
+        <v>17</v>
+      </c>
+      <c r="N65" t="s">
+        <v>335</v>
+      </c>
+      <c r="O65" t="s">
+        <v>336</v>
+      </c>
+      <c r="P65" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>35</v>
+      </c>
+      <c r="R65" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="66" spans="13:18">
+      <c r="M66" t="s">
+        <v>17</v>
+      </c>
+      <c r="N66" t="s">
+        <v>337</v>
+      </c>
+      <c r="O66" t="s">
+        <v>338</v>
+      </c>
+      <c r="P66" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>35</v>
+      </c>
+      <c r="R66" t="s">
         <v>216</v>
       </c>
     </row>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122B39E6-8006-42DF-8ED4-7D0B738AD240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C51860E5-D212-4B70-BF2E-0ED271B1287D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -5066,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51CF4A75-A2F4-4AB9-B852-3088D3B7DF51}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C1468A1-FA55-454F-A138-52EB65FC019C}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C51860E5-D212-4B70-BF2E-0ED271B1287D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9772589B-1775-465C-8555-98C55D5912B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="21600" windowHeight="12683" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -5066,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C1468A1-FA55-454F-A138-52EB65FC019C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E00895CE-1FD6-4CCA-AF48-A51A046EEE5A}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9772589B-1775-465C-8555-98C55D5912B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6AEA30-8ED2-490B-849A-153C6DBB9506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="21600" windowHeight="12683" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -833,115 +833,115 @@
     <t>elc_wof_001</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 1</t>
+    <t>wind offshore electricity generation in cluster -- 1</t>
   </si>
   <si>
     <t>elc_wof_002</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 2</t>
+    <t>wind offshore electricity generation in cluster -- 2</t>
   </si>
   <si>
     <t>elc_wof_003</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 3</t>
+    <t>wind offshore electricity generation in cluster -- 3</t>
   </si>
   <si>
     <t>elc_wof_004</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 4</t>
+    <t>wind offshore electricity generation in cluster -- 4</t>
   </si>
   <si>
     <t>elc_wof_005</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 5</t>
+    <t>wind offshore electricity generation in cluster -- 5</t>
   </si>
   <si>
     <t>elc_wof_006</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 6</t>
+    <t>wind offshore electricity generation in cluster -- 6</t>
   </si>
   <si>
     <t>elc_wof_007</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 7</t>
+    <t>wind offshore electricity generation in cluster -- 7</t>
   </si>
   <si>
     <t>elc_wof_008</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 8</t>
+    <t>wind offshore electricity generation in cluster -- 8</t>
   </si>
   <si>
     <t>elc_wof_009</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 9</t>
+    <t>wind offshore electricity generation in cluster -- 9</t>
   </si>
   <si>
     <t>elc_wof_010</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 10</t>
+    <t>wind offshore electricity generation in cluster -- 10</t>
   </si>
   <si>
     <t>elc_wof_011</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 11</t>
+    <t>wind offshore electricity generation in cluster -- 11</t>
   </si>
   <si>
     <t>elc_wof_012</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 12</t>
+    <t>wind offshore electricity generation in cluster -- 12</t>
   </si>
   <si>
     <t>elc_wof_013</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 13</t>
+    <t>wind offshore electricity generation in cluster -- 13</t>
   </si>
   <si>
     <t>elc_wof_014</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 14</t>
+    <t>wind offshore electricity generation in cluster -- 14</t>
   </si>
   <si>
     <t>elc_wof_015</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 15</t>
+    <t>wind offshore electricity generation in cluster -- 15</t>
   </si>
   <si>
     <t>elc_wof_016</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 16</t>
+    <t>wind offshore electricity generation in cluster -- 16</t>
   </si>
   <si>
     <t>elc_wof_017</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 17</t>
+    <t>wind offshore electricity generation in cluster -- 17</t>
   </si>
   <si>
     <t>elc_wof_018</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 18</t>
+    <t>wind offshore electricity generation in cluster -- 18</t>
   </si>
   <si>
     <t>elc_wof_019</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 19</t>
+    <t>wind offshore electricity generation in cluster -- 19</t>
   </si>
   <si>
     <t>elc_won_001</t>
@@ -5066,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E00895CE-1FD6-4CCA-AF48-A51A046EEE5A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75C0B873-6247-43D8-9E73-2F720199CCAE}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6AEA30-8ED2-490B-849A-153C6DBB9506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB2D5C0-8C6E-433D-A114-4E3412972074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="21600" windowHeight="12683" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -5066,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75C0B873-6247-43D8-9E73-2F720199CCAE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D45F54-6239-40D4-A0B5-B66702E0B164}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB2D5C0-8C6E-433D-A114-4E3412972074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA3C4DD9-83B3-4959-BEFE-710C7551BB49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="21600" windowHeight="12683" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -5066,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D45F54-6239-40D4-A0B5-B66702E0B164}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F18E74F-8E05-4E54-B72D-1506754E34A9}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA3C4DD9-83B3-4959-BEFE-710C7551BB49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CA2660B-C3BE-49A2-8CC0-6474F6182B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5066,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F18E74F-8E05-4E54-B72D-1506754E34A9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55074C57-4289-4488-8993-A2478924C6AB}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CA2660B-C3BE-49A2-8CC0-6474F6182B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ECC5126-75C1-4D53-97DA-D578F7D3E4CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5066,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55074C57-4289-4488-8993-A2478924C6AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1569D6C-7D65-466C-9803-0E847A67A4D1}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ECC5126-75C1-4D53-97DA-D578F7D3E4CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F27E012-4034-485F-9D4B-59A8AD96B64F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5066,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1569D6C-7D65-466C-9803-0E847A67A4D1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE47CE7F-EC74-4C43-8BE6-7D45BAA68955}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F27E012-4034-485F-9D4B-59A8AD96B64F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB34650-0D30-4075-9CF3-055CC7D75E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5066,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE47CE7F-EC74-4C43-8BE6-7D45BAA68955}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5286CD8B-4F2E-47BE-BDA4-48067FCAE3B5}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB34650-0D30-4075-9CF3-055CC7D75E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69B873F8-F6CA-42B8-8954-CF478D963573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5066,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5286CD8B-4F2E-47BE-BDA4-48067FCAE3B5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D88BF63-FDFF-4976-AA1F-00800C24CCF8}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69B873F8-F6CA-42B8-8954-CF478D963573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32ABA2E6-5CA3-4E6F-B0FA-A90633C39352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5066,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D88BF63-FDFF-4976-AA1F-00800C24CCF8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54AEFCA6-3C07-43F7-BBF5-39C2E5742D5A}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32ABA2E6-5CA3-4E6F-B0FA-A90633C39352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854F7328-8DF6-41DB-AE6E-F6C3107CAA88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5066,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54AEFCA6-3C07-43F7-BBF5-39C2E5742D5A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FE8792F-7BE6-476F-AD92-A87B029EDCCC}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854F7328-8DF6-41DB-AE6E-F6C3107CAA88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF807AA-5FF0-40A2-8D7A-DF68C136F7A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5066,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FE8792F-7BE6-476F-AD92-A87B029EDCCC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95AF7046-42FE-45BD-820D-99D345956533}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF807AA-5FF0-40A2-8D7A-DF68C136F7A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58773B1E-FCA8-409D-917E-9CAAF1808C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5066,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95AF7046-42FE-45BD-820D-99D345956533}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00379879-9340-42DA-B63C-E45AFC519AD9}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58773B1E-FCA8-409D-917E-9CAAF1808C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B639BDBE-56E8-44E1-90A8-3FA37DD9622C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -5066,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00379879-9340-42DA-B63C-E45AFC519AD9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A420D8B8-FD1F-40FC-AA55-B2EA37BF567A}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B639BDBE-56E8-44E1-90A8-3FA37DD9622C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C26F4A5-DF8D-4E4E-A28E-7D5A6D59D6B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -5066,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A420D8B8-FD1F-40FC-AA55-B2EA37BF567A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29E71CE5-0673-4982-8F49-7CDF631C622C}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C26F4A5-DF8D-4E4E-A28E-7D5A6D59D6B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC35EE2-519D-4731-B100-234B16D85B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -5066,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29E71CE5-0673-4982-8F49-7CDF631C622C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBC9FCEA-629E-4A87-8C95-A70E76308B82}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC35EE2-519D-4731-B100-234B16D85B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B9CFFA-B1A8-4A77-96FD-22A39E2A4B89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -5066,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBC9FCEA-629E-4A87-8C95-A70E76308B82}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A444B959-CE64-472D-97BA-ED336E098DC8}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B9CFFA-B1A8-4A77-96FD-22A39E2A4B89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4210F65C-8423-45A6-A3BF-9B9D1A87FB0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5066,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A444B959-CE64-472D-97BA-ED336E098DC8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2482B15B-6B93-43BC-B81D-646EDFB87E22}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4210F65C-8423-45A6-A3BF-9B9D1A87FB0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C215311C-E1C8-410A-BAA4-E117B8513910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5066,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2482B15B-6B93-43BC-B81D-646EDFB87E22}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2537D366-008F-4BF8-8DD6-7D72DED68B97}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C215311C-E1C8-410A-BAA4-E117B8513910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC5B2D8-04D7-49EB-8417-87CF83807C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5066,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2537D366-008F-4BF8-8DD6-7D72DED68B97}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8B6F4BE-1FB0-4614-AA3C-8F2DD91FF253}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC5B2D8-04D7-49EB-8417-87CF83807C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB0E69B-8C82-46F4-BC48-1D978055C584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5066,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8B6F4BE-1FB0-4614-AA3C-8F2DD91FF253}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43BE780B-DBDF-4A1A-803F-E729E4AD3837}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB0E69B-8C82-46F4-BC48-1D978055C584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B2C17E-31B9-4B35-A044-2C2F1A100D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5066,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43BE780B-DBDF-4A1A-803F-E729E4AD3837}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{911E0C59-865A-4C92-80B0-1D8A131CC813}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B2C17E-31B9-4B35-A044-2C2F1A100D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A925A7AE-55F4-4938-AE46-798B21364F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5066,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{911E0C59-865A-4C92-80B0-1D8A131CC813}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15ADDAD6-BF07-48B3-AE74-F676C0DB6C57}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A925A7AE-55F4-4938-AE46-798B21364F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72DD95EF-8852-4545-B071-A39C337C7DBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5066,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15ADDAD6-BF07-48B3-AE74-F676C0DB6C57}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4428527E-A978-45B9-913F-992CE60B1B02}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72DD95EF-8852-4545-B071-A39C337C7DBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0D7057B-AFCD-49AA-841B-2D86E3DFB777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5066,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4428527E-A978-45B9-913F-992CE60B1B02}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87235C92-8EF6-457F-B55B-C70A944485F6}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0D7057B-AFCD-49AA-841B-2D86E3DFB777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC101EC-E5C8-467B-9786-35C796317CCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5066,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87235C92-8EF6-457F-B55B-C70A944485F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D365D38-082D-4841-A110-D5C08DBDD808}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038E5048-A1C6-40AF-8B2E-7939564DDCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0FD7639-9944-45B4-B6D5-B6875D3FD6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -6895,7 +6895,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{703D63A3-6C99-4851-8E9A-2D083DBDD6D0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AE8698B-91E4-46FE-B07C-21244A1B770D}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0FD7639-9944-45B4-B6D5-B6875D3FD6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D079148E-A13F-44AF-9A55-EF0652AD7D4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6895,7 +6895,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AE8698B-91E4-46FE-B07C-21244A1B770D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56EAC6D6-4007-4277-8D29-44E3485D3AA8}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SysSettings.xlsx
+++ b/VerveStacks_ITA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D079148E-A13F-44AF-9A55-EF0652AD7D4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D500523-8FF3-43E9-9157-3F802CF2B8DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6895,7 +6895,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56EAC6D6-4007-4277-8D29-44E3485D3AA8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F211AA2F-FF14-4FC3-BAFE-E6E105ADC0D8}">
   <dimension ref="B3:H269"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
